--- a/examples/Methylene Blue Diffusion Parameter Fitting/dialysis_tubing_diffusion_data.xlsx
+++ b/examples/Methylene Blue Diffusion Parameter Fitting/dialysis_tubing_diffusion_data.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wille\Desktop\FVMFramework\examples\Methylene Blue Diffusion Parameter Fitting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523BACDF-E576-45E0-9CE5-B47F3DF658D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AF8915-C635-4ED4-AA99-2A5FE77BD952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="2" xr2:uid="{C8BDC4CA-D246-4F0A-BCDF-D03343993973}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="5" xr2:uid="{C8BDC4CA-D246-4F0A-BCDF-D03343993973}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="calibration" sheetId="3" r:id="rId2"/>
     <sheet name="T1" sheetId="2" r:id="rId3"/>
     <sheet name="T1 Temps" sheetId="4" r:id="rId4"/>
+    <sheet name="T2" sheetId="5" r:id="rId5"/>
+    <sheet name="T3" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>calibration stocks</t>
   </si>
@@ -67,13 +69,44 @@
   <si>
     <t>temp (*C)</t>
   </si>
+  <si>
+    <t>additional notes</t>
+  </si>
+  <si>
+    <t>500 rpm stir bar</t>
+  </si>
+  <si>
+    <t>It's consistent!</t>
+  </si>
+  <si>
+    <t>6.5 cm of dialysis tubing covered</t>
+  </si>
+  <si>
+    <t>2.0 cm OD</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>It's not consistent :(</t>
+  </si>
+  <si>
+    <t>we're going to have to go back and check the logs</t>
+  </si>
+  <si>
+    <t>This or the one before should not be trusted</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -127,13 +160,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,61 +586,93 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{997B9970-4CFF-4D2E-86B1-D105EC24C029}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.47265625" customWidth="1"/>
+    <col min="4" max="4" width="12.47265625" customWidth="1"/>
+    <col min="6" max="6" width="17.20703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5">
         <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E2">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5">
         <v>0.25</v>
       </c>
       <c r="B3">
         <v>0.127</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3">
+        <v>0.127</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>0.5</v>
       </c>
       <c r="B4">
         <v>0.28599999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E4">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5">
         <v>0.75</v>
       </c>
       <c r="B5">
         <v>0.41199999999999998</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6">
         <v>0.57599999999999996</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E6">
+        <v>0.58799999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5"/>
     </row>
   </sheetData>
@@ -617,60 +682,114 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C218C657-FA30-4DE9-AFA1-3986854EA20E}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.47265625" customWidth="1"/>
     <col min="2" max="2" width="10.578125" customWidth="1"/>
+    <col min="7" max="7" width="15.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6">
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6">
-        <v>20</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6">
-        <v>30</v>
-      </c>
-      <c r="B5" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6">
-        <v>40</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0.2</v>
-      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.113</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.318</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.38400000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -686,7 +805,7 @@
       <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -694,7 +813,7 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>50</v>
       </c>
     </row>
@@ -702,7 +821,7 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>50</v>
       </c>
     </row>
@@ -710,7 +829,7 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -718,7 +837,7 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -726,7 +845,7 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -734,7 +853,7 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -742,7 +861,7 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -750,7 +869,7 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -758,7 +877,7 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -766,7 +885,7 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -774,7 +893,7 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -782,7 +901,7 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -790,7 +909,7 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -798,7 +917,7 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -806,7 +925,7 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -814,7 +933,7 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -822,7 +941,7 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -830,7 +949,7 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -838,7 +957,7 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -846,7 +965,7 @@
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -854,7 +973,7 @@
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -862,7 +981,7 @@
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -870,7 +989,7 @@
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -878,7 +997,7 @@
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -886,7 +1005,7 @@
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -894,7 +1013,7 @@
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -902,7 +1021,7 @@
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -910,7 +1029,7 @@
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -918,7 +1037,7 @@
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -926,7 +1045,7 @@
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -934,7 +1053,7 @@
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -942,7 +1061,7 @@
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -950,7 +1069,7 @@
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -958,7 +1077,7 @@
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -966,7 +1085,7 @@
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -974,7 +1093,7 @@
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -982,7 +1101,7 @@
       <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -990,7 +1109,7 @@
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -998,7 +1117,7 @@
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1006,7 +1125,7 @@
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1014,7 +1133,7 @@
       <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1022,7 +1141,7 @@
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1030,7 +1149,7 @@
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1038,7 +1157,7 @@
       <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1046,7 +1165,7 @@
       <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="7">
         <v>49</v>
       </c>
     </row>
@@ -1054,7 +1173,7 @@
       <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -1062,7 +1181,7 @@
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -1070,7 +1189,7 @@
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -1078,7 +1197,7 @@
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -1086,7 +1205,7 @@
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -1094,7 +1213,7 @@
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1102,7 +1221,7 @@
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1110,7 +1229,7 @@
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1118,7 +1237,7 @@
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1126,7 +1245,7 @@
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1134,7 +1253,7 @@
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1142,7 +1261,7 @@
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1150,7 +1269,7 @@
       <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -1158,7 +1277,7 @@
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1166,7 +1285,7 @@
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1174,7 +1293,7 @@
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1182,7 +1301,7 @@
       <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1190,7 +1309,7 @@
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1198,7 +1317,7 @@
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1206,7 +1325,7 @@
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -1214,7 +1333,7 @@
       <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -1222,7 +1341,7 @@
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -1230,7 +1349,7 @@
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -1238,7 +1357,7 @@
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -1246,7 +1365,7 @@
       <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -1254,7 +1373,7 @@
       <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1262,7 +1381,7 @@
       <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1270,7 +1389,7 @@
       <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1278,7 +1397,7 @@
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1286,7 +1405,7 @@
       <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1294,7 +1413,7 @@
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1302,7 +1421,7 @@
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1310,7 +1429,7 @@
       <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1318,7 +1437,7 @@
       <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1326,7 +1445,7 @@
       <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1334,7 +1453,7 @@
       <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1342,7 +1461,7 @@
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1350,7 +1469,7 @@
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" s="8">
+      <c r="B84" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1358,7 +1477,7 @@
       <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1366,7 +1485,7 @@
       <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" s="8">
+      <c r="B86" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1374,7 +1493,7 @@
       <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B87" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -1382,7 +1501,7 @@
       <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B88" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1390,7 +1509,7 @@
       <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B89" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1398,7 +1517,7 @@
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1406,7 +1525,7 @@
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1414,7 +1533,7 @@
       <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1422,7 +1541,7 @@
       <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1430,7 +1549,7 @@
       <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1438,7 +1557,7 @@
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1446,7 +1565,7 @@
       <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1454,7 +1573,7 @@
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1462,7 +1581,7 @@
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1470,7 +1589,7 @@
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -1478,7 +1597,7 @@
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1486,7 +1605,7 @@
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1494,7 +1613,7 @@
       <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1502,7 +1621,7 @@
       <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1510,7 +1629,7 @@
       <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1518,7 +1637,7 @@
       <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" s="8">
+      <c r="B105" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1526,7 +1645,7 @@
       <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" s="8">
+      <c r="B106" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1534,7 +1653,7 @@
       <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" s="8">
+      <c r="B107" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1542,7 +1661,7 @@
       <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" s="8">
+      <c r="B108" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1550,7 +1669,7 @@
       <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" s="8">
+      <c r="B109" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -1558,7 +1677,7 @@
       <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" s="8">
+      <c r="B110" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1566,7 +1685,7 @@
       <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" s="8">
+      <c r="B111" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1574,7 +1693,7 @@
       <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" s="8">
+      <c r="B112" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1582,7 +1701,7 @@
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" s="8">
+      <c r="B113" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1590,7 +1709,7 @@
       <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" s="8">
+      <c r="B114" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1598,7 +1717,7 @@
       <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" s="8">
+      <c r="B115" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1606,7 +1725,7 @@
       <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1614,7 +1733,7 @@
       <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" s="8">
+      <c r="B117" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1622,7 +1741,7 @@
       <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" s="8">
+      <c r="B118" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1630,7 +1749,7 @@
       <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" s="8">
+      <c r="B119" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1638,7 +1757,7 @@
       <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" s="8">
+      <c r="B120" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1646,7 +1765,7 @@
       <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" s="8">
+      <c r="B121" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1654,7 +1773,7 @@
       <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" s="8">
+      <c r="B122" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1662,7 +1781,7 @@
       <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" s="8">
+      <c r="B123" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1670,7 +1789,7 @@
       <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" s="8">
+      <c r="B124" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1678,7 +1797,7 @@
       <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" s="8">
+      <c r="B125" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -1686,7 +1805,7 @@
       <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" s="8">
+      <c r="B126" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1694,7 +1813,7 @@
       <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" s="8">
+      <c r="B127" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1702,7 +1821,7 @@
       <c r="A128">
         <v>126</v>
       </c>
-      <c r="B128" s="8">
+      <c r="B128" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1710,7 +1829,7 @@
       <c r="A129">
         <v>127</v>
       </c>
-      <c r="B129" s="8">
+      <c r="B129" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1718,7 +1837,7 @@
       <c r="A130">
         <v>128</v>
       </c>
-      <c r="B130" s="8">
+      <c r="B130" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1726,7 +1845,7 @@
       <c r="A131">
         <v>129</v>
       </c>
-      <c r="B131" s="8">
+      <c r="B131" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1734,7 +1853,7 @@
       <c r="A132">
         <v>130</v>
       </c>
-      <c r="B132" s="8">
+      <c r="B132" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1742,7 +1861,7 @@
       <c r="A133">
         <v>131</v>
       </c>
-      <c r="B133" s="8">
+      <c r="B133" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1750,7 +1869,7 @@
       <c r="A134">
         <v>132</v>
       </c>
-      <c r="B134" s="8">
+      <c r="B134" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1758,7 +1877,7 @@
       <c r="A135">
         <v>133</v>
       </c>
-      <c r="B135" s="8">
+      <c r="B135" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1766,7 +1885,7 @@
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" s="8">
+      <c r="B136" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1774,7 +1893,7 @@
       <c r="A137">
         <v>135</v>
       </c>
-      <c r="B137" s="8">
+      <c r="B137" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1782,7 +1901,7 @@
       <c r="A138">
         <v>136</v>
       </c>
-      <c r="B138" s="8">
+      <c r="B138" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1790,7 +1909,7 @@
       <c r="A139">
         <v>137</v>
       </c>
-      <c r="B139" s="8">
+      <c r="B139" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1798,7 +1917,7 @@
       <c r="A140">
         <v>138</v>
       </c>
-      <c r="B140" s="8">
+      <c r="B140" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1806,7 +1925,7 @@
       <c r="A141">
         <v>139</v>
       </c>
-      <c r="B141" s="8">
+      <c r="B141" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1814,7 +1933,7 @@
       <c r="A142">
         <v>140</v>
       </c>
-      <c r="B142" s="8">
+      <c r="B142" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1822,7 +1941,7 @@
       <c r="A143">
         <v>141</v>
       </c>
-      <c r="B143" s="8">
+      <c r="B143" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -1830,7 +1949,7 @@
       <c r="A144">
         <v>142</v>
       </c>
-      <c r="B144" s="8">
+      <c r="B144" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1838,7 +1957,7 @@
       <c r="A145">
         <v>143</v>
       </c>
-      <c r="B145" s="8">
+      <c r="B145" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1846,7 +1965,7 @@
       <c r="A146">
         <v>144</v>
       </c>
-      <c r="B146" s="8">
+      <c r="B146" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1854,7 +1973,7 @@
       <c r="A147">
         <v>145</v>
       </c>
-      <c r="B147" s="8">
+      <c r="B147" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1862,7 +1981,7 @@
       <c r="A148">
         <v>146</v>
       </c>
-      <c r="B148" s="8">
+      <c r="B148" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1870,7 +1989,7 @@
       <c r="A149">
         <v>147</v>
       </c>
-      <c r="B149" s="8">
+      <c r="B149" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1878,7 +1997,7 @@
       <c r="A150">
         <v>148</v>
       </c>
-      <c r="B150" s="8">
+      <c r="B150" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1886,7 +2005,7 @@
       <c r="A151">
         <v>149</v>
       </c>
-      <c r="B151" s="8">
+      <c r="B151" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1894,7 +2013,7 @@
       <c r="A152">
         <v>150</v>
       </c>
-      <c r="B152" s="8">
+      <c r="B152" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1902,7 +2021,7 @@
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" s="8">
+      <c r="B153" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1910,7 +2029,7 @@
       <c r="A154">
         <v>152</v>
       </c>
-      <c r="B154" s="8">
+      <c r="B154" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1918,7 +2037,7 @@
       <c r="A155">
         <v>153</v>
       </c>
-      <c r="B155" s="8">
+      <c r="B155" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1926,7 +2045,7 @@
       <c r="A156">
         <v>154</v>
       </c>
-      <c r="B156" s="8">
+      <c r="B156" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1934,7 +2053,7 @@
       <c r="A157">
         <v>155</v>
       </c>
-      <c r="B157" s="8">
+      <c r="B157" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1942,7 +2061,7 @@
       <c r="A158">
         <v>156</v>
       </c>
-      <c r="B158" s="8">
+      <c r="B158" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1950,7 +2069,7 @@
       <c r="A159">
         <v>157</v>
       </c>
-      <c r="B159" s="8">
+      <c r="B159" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1958,7 +2077,7 @@
       <c r="A160">
         <v>158</v>
       </c>
-      <c r="B160" s="8">
+      <c r="B160" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1966,7 +2085,7 @@
       <c r="A161">
         <v>159</v>
       </c>
-      <c r="B161" s="8">
+      <c r="B161" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1974,7 +2093,7 @@
       <c r="A162">
         <v>160</v>
       </c>
-      <c r="B162" s="8">
+      <c r="B162" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1982,7 +2101,7 @@
       <c r="A163">
         <v>161</v>
       </c>
-      <c r="B163" s="8">
+      <c r="B163" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1990,7 +2109,7 @@
       <c r="A164">
         <v>162</v>
       </c>
-      <c r="B164" s="8">
+      <c r="B164" s="7">
         <v>48</v>
       </c>
     </row>
@@ -1998,7 +2117,7 @@
       <c r="A165">
         <v>163</v>
       </c>
-      <c r="B165" s="8">
+      <c r="B165" s="7">
         <v>48</v>
       </c>
     </row>
@@ -2006,7 +2125,7 @@
       <c r="A166">
         <v>164</v>
       </c>
-      <c r="B166" s="8">
+      <c r="B166" s="7">
         <v>48</v>
       </c>
     </row>
@@ -2014,7 +2133,7 @@
       <c r="A167">
         <v>165</v>
       </c>
-      <c r="B167" s="8">
+      <c r="B167" s="7">
         <v>48</v>
       </c>
     </row>
@@ -2022,7 +2141,7 @@
       <c r="A168">
         <v>166</v>
       </c>
-      <c r="B168" s="8">
+      <c r="B168" s="7">
         <v>48</v>
       </c>
     </row>
@@ -2030,7 +2149,7 @@
       <c r="A169">
         <v>167</v>
       </c>
-      <c r="B169" s="8">
+      <c r="B169" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2038,7 +2157,7 @@
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" s="8">
+      <c r="B170" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2046,7 +2165,7 @@
       <c r="A171">
         <v>169</v>
       </c>
-      <c r="B171" s="8">
+      <c r="B171" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2054,7 +2173,7 @@
       <c r="A172">
         <v>170</v>
       </c>
-      <c r="B172" s="8">
+      <c r="B172" s="7">
         <v>48</v>
       </c>
     </row>
@@ -2062,7 +2181,7 @@
       <c r="A173">
         <v>171</v>
       </c>
-      <c r="B173" s="8">
+      <c r="B173" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2070,7 +2189,7 @@
       <c r="A174">
         <v>172</v>
       </c>
-      <c r="B174" s="8">
+      <c r="B174" s="7">
         <v>48</v>
       </c>
     </row>
@@ -2078,7 +2197,7 @@
       <c r="A175">
         <v>173</v>
       </c>
-      <c r="B175" s="8">
+      <c r="B175" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2086,7 +2205,7 @@
       <c r="A176">
         <v>174</v>
       </c>
-      <c r="B176" s="8">
+      <c r="B176" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2094,7 +2213,7 @@
       <c r="A177">
         <v>175</v>
       </c>
-      <c r="B177" s="8">
+      <c r="B177" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2102,7 +2221,7 @@
       <c r="A178">
         <v>176</v>
       </c>
-      <c r="B178" s="8">
+      <c r="B178" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2110,7 +2229,7 @@
       <c r="A179">
         <v>177</v>
       </c>
-      <c r="B179" s="8">
+      <c r="B179" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2118,7 +2237,7 @@
       <c r="A180">
         <v>178</v>
       </c>
-      <c r="B180" s="8">
+      <c r="B180" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2126,7 +2245,7 @@
       <c r="A181">
         <v>179</v>
       </c>
-      <c r="B181" s="8">
+      <c r="B181" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2134,7 +2253,7 @@
       <c r="A182">
         <v>180</v>
       </c>
-      <c r="B182" s="8">
+      <c r="B182" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2142,7 +2261,7 @@
       <c r="A183">
         <v>181</v>
       </c>
-      <c r="B183" s="8">
+      <c r="B183" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2150,7 +2269,7 @@
       <c r="A184">
         <v>182</v>
       </c>
-      <c r="B184" s="8">
+      <c r="B184" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2158,7 +2277,7 @@
       <c r="A185">
         <v>183</v>
       </c>
-      <c r="B185" s="8">
+      <c r="B185" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2166,7 +2285,7 @@
       <c r="A186">
         <v>184</v>
       </c>
-      <c r="B186" s="8">
+      <c r="B186" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2174,7 +2293,7 @@
       <c r="A187">
         <v>185</v>
       </c>
-      <c r="B187" s="8">
+      <c r="B187" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2182,7 +2301,7 @@
       <c r="A188">
         <v>186</v>
       </c>
-      <c r="B188" s="8">
+      <c r="B188" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2190,7 +2309,7 @@
       <c r="A189">
         <v>187</v>
       </c>
-      <c r="B189" s="8">
+      <c r="B189" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2198,7 +2317,7 @@
       <c r="A190">
         <v>188</v>
       </c>
-      <c r="B190" s="8">
+      <c r="B190" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2206,7 +2325,7 @@
       <c r="A191">
         <v>189</v>
       </c>
-      <c r="B191" s="8">
+      <c r="B191" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2214,7 +2333,7 @@
       <c r="A192">
         <v>190</v>
       </c>
-      <c r="B192" s="8">
+      <c r="B192" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2222,7 +2341,7 @@
       <c r="A193">
         <v>191</v>
       </c>
-      <c r="B193" s="8">
+      <c r="B193" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2230,7 +2349,7 @@
       <c r="A194">
         <v>192</v>
       </c>
-      <c r="B194" s="8">
+      <c r="B194" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2238,7 +2357,7 @@
       <c r="A195">
         <v>193</v>
       </c>
-      <c r="B195" s="8">
+      <c r="B195" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2246,7 +2365,7 @@
       <c r="A196">
         <v>194</v>
       </c>
-      <c r="B196" s="8">
+      <c r="B196" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2254,7 +2373,7 @@
       <c r="A197">
         <v>195</v>
       </c>
-      <c r="B197" s="8">
+      <c r="B197" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2262,7 +2381,7 @@
       <c r="A198">
         <v>196</v>
       </c>
-      <c r="B198" s="8">
+      <c r="B198" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2270,7 +2389,7 @@
       <c r="A199">
         <v>197</v>
       </c>
-      <c r="B199" s="8">
+      <c r="B199" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2278,7 +2397,7 @@
       <c r="A200">
         <v>198</v>
       </c>
-      <c r="B200" s="8">
+      <c r="B200" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2286,7 +2405,7 @@
       <c r="A201">
         <v>199</v>
       </c>
-      <c r="B201" s="8">
+      <c r="B201" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2294,7 +2413,7 @@
       <c r="A202">
         <v>200</v>
       </c>
-      <c r="B202" s="8">
+      <c r="B202" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2302,7 +2421,7 @@
       <c r="A203">
         <v>201</v>
       </c>
-      <c r="B203" s="8">
+      <c r="B203" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2310,7 +2429,7 @@
       <c r="A204">
         <v>202</v>
       </c>
-      <c r="B204" s="8">
+      <c r="B204" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2318,7 +2437,7 @@
       <c r="A205">
         <v>203</v>
       </c>
-      <c r="B205" s="8">
+      <c r="B205" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2326,7 +2445,7 @@
       <c r="A206">
         <v>204</v>
       </c>
-      <c r="B206" s="8">
+      <c r="B206" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -2334,7 +2453,7 @@
       <c r="A207">
         <v>205</v>
       </c>
-      <c r="B207" s="8">
+      <c r="B207" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2342,7 +2461,7 @@
       <c r="A208">
         <v>206</v>
       </c>
-      <c r="B208" s="8">
+      <c r="B208" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2350,7 +2469,7 @@
       <c r="A209">
         <v>207</v>
       </c>
-      <c r="B209" s="8">
+      <c r="B209" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2358,7 +2477,7 @@
       <c r="A210">
         <v>208</v>
       </c>
-      <c r="B210" s="8">
+      <c r="B210" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2366,7 +2485,7 @@
       <c r="A211">
         <v>209</v>
       </c>
-      <c r="B211" s="8">
+      <c r="B211" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2374,7 +2493,7 @@
       <c r="A212">
         <v>210</v>
       </c>
-      <c r="B212" s="8">
+      <c r="B212" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2382,7 +2501,7 @@
       <c r="A213">
         <v>211</v>
       </c>
-      <c r="B213" s="8">
+      <c r="B213" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2390,7 +2509,7 @@
       <c r="A214">
         <v>212</v>
       </c>
-      <c r="B214" s="8">
+      <c r="B214" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2398,7 +2517,7 @@
       <c r="A215">
         <v>213</v>
       </c>
-      <c r="B215" s="8">
+      <c r="B215" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2406,7 +2525,7 @@
       <c r="A216">
         <v>214</v>
       </c>
-      <c r="B216" s="8">
+      <c r="B216" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2414,7 +2533,7 @@
       <c r="A217">
         <v>215</v>
       </c>
-      <c r="B217" s="8">
+      <c r="B217" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2422,7 +2541,7 @@
       <c r="A218">
         <v>216</v>
       </c>
-      <c r="B218" s="8">
+      <c r="B218" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2430,7 +2549,7 @@
       <c r="A219">
         <v>217</v>
       </c>
-      <c r="B219" s="8">
+      <c r="B219" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2438,7 +2557,7 @@
       <c r="A220">
         <v>218</v>
       </c>
-      <c r="B220" s="8">
+      <c r="B220" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2446,7 +2565,7 @@
       <c r="A221">
         <v>219</v>
       </c>
-      <c r="B221" s="8">
+      <c r="B221" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2454,7 +2573,7 @@
       <c r="A222">
         <v>220</v>
       </c>
-      <c r="B222" s="8">
+      <c r="B222" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2462,7 +2581,7 @@
       <c r="A223">
         <v>221</v>
       </c>
-      <c r="B223" s="8">
+      <c r="B223" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2470,7 +2589,7 @@
       <c r="A224">
         <v>222</v>
       </c>
-      <c r="B224" s="8">
+      <c r="B224" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2478,7 +2597,7 @@
       <c r="A225">
         <v>223</v>
       </c>
-      <c r="B225" s="8">
+      <c r="B225" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2486,7 +2605,7 @@
       <c r="A226">
         <v>224</v>
       </c>
-      <c r="B226" s="8">
+      <c r="B226" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2494,7 +2613,7 @@
       <c r="A227">
         <v>225</v>
       </c>
-      <c r="B227" s="8">
+      <c r="B227" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2502,7 +2621,7 @@
       <c r="A228">
         <v>226</v>
       </c>
-      <c r="B228" s="8">
+      <c r="B228" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2510,7 +2629,7 @@
       <c r="A229">
         <v>227</v>
       </c>
-      <c r="B229" s="8">
+      <c r="B229" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2518,7 +2637,7 @@
       <c r="A230">
         <v>228</v>
       </c>
-      <c r="B230" s="8">
+      <c r="B230" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2526,7 +2645,7 @@
       <c r="A231">
         <v>229</v>
       </c>
-      <c r="B231" s="8">
+      <c r="B231" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2534,7 +2653,7 @@
       <c r="A232">
         <v>230</v>
       </c>
-      <c r="B232" s="8">
+      <c r="B232" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2542,7 +2661,7 @@
       <c r="A233">
         <v>231</v>
       </c>
-      <c r="B233" s="8">
+      <c r="B233" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2550,7 +2669,7 @@
       <c r="A234">
         <v>232</v>
       </c>
-      <c r="B234" s="8">
+      <c r="B234" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2558,7 +2677,7 @@
       <c r="A235">
         <v>233</v>
       </c>
-      <c r="B235" s="8">
+      <c r="B235" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2566,7 +2685,7 @@
       <c r="A236">
         <v>234</v>
       </c>
-      <c r="B236" s="8">
+      <c r="B236" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2574,7 +2693,7 @@
       <c r="A237">
         <v>235</v>
       </c>
-      <c r="B237" s="8">
+      <c r="B237" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2582,7 +2701,7 @@
       <c r="A238">
         <v>236</v>
       </c>
-      <c r="B238" s="8">
+      <c r="B238" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2590,7 +2709,7 @@
       <c r="A239">
         <v>237</v>
       </c>
-      <c r="B239" s="8">
+      <c r="B239" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2598,7 +2717,7 @@
       <c r="A240">
         <v>238</v>
       </c>
-      <c r="B240" s="8">
+      <c r="B240" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2606,7 +2725,7 @@
       <c r="A241">
         <v>239</v>
       </c>
-      <c r="B241" s="8">
+      <c r="B241" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2614,7 +2733,7 @@
       <c r="A242">
         <v>240</v>
       </c>
-      <c r="B242" s="8">
+      <c r="B242" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2622,7 +2741,7 @@
       <c r="A243">
         <v>241</v>
       </c>
-      <c r="B243" s="8">
+      <c r="B243" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2630,7 +2749,7 @@
       <c r="A244">
         <v>242</v>
       </c>
-      <c r="B244" s="8">
+      <c r="B244" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2638,7 +2757,7 @@
       <c r="A245">
         <v>243</v>
       </c>
-      <c r="B245" s="8">
+      <c r="B245" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2646,7 +2765,7 @@
       <c r="A246">
         <v>244</v>
       </c>
-      <c r="B246" s="8">
+      <c r="B246" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2654,7 +2773,7 @@
       <c r="A247">
         <v>245</v>
       </c>
-      <c r="B247" s="8">
+      <c r="B247" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2662,7 +2781,7 @@
       <c r="A248">
         <v>246</v>
       </c>
-      <c r="B248" s="8">
+      <c r="B248" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2670,7 +2789,7 @@
       <c r="A249">
         <v>247</v>
       </c>
-      <c r="B249" s="8">
+      <c r="B249" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2678,7 +2797,7 @@
       <c r="A250">
         <v>248</v>
       </c>
-      <c r="B250" s="8">
+      <c r="B250" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2686,7 +2805,7 @@
       <c r="A251">
         <v>249</v>
       </c>
-      <c r="B251" s="8">
+      <c r="B251" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2694,7 +2813,7 @@
       <c r="A252">
         <v>250</v>
       </c>
-      <c r="B252" s="8">
+      <c r="B252" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2702,7 +2821,7 @@
       <c r="A253">
         <v>251</v>
       </c>
-      <c r="B253" s="8">
+      <c r="B253" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2710,7 +2829,7 @@
       <c r="A254">
         <v>252</v>
       </c>
-      <c r="B254" s="8">
+      <c r="B254" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2718,7 +2837,7 @@
       <c r="A255">
         <v>253</v>
       </c>
-      <c r="B255" s="8">
+      <c r="B255" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2726,7 +2845,7 @@
       <c r="A256">
         <v>254</v>
       </c>
-      <c r="B256" s="8">
+      <c r="B256" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2734,7 +2853,7 @@
       <c r="A257">
         <v>255</v>
       </c>
-      <c r="B257" s="8">
+      <c r="B257" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2742,7 +2861,7 @@
       <c r="A258">
         <v>256</v>
       </c>
-      <c r="B258" s="8">
+      <c r="B258" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2750,7 +2869,7 @@
       <c r="A259">
         <v>257</v>
       </c>
-      <c r="B259" s="8">
+      <c r="B259" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2758,7 +2877,7 @@
       <c r="A260">
         <v>258</v>
       </c>
-      <c r="B260" s="8">
+      <c r="B260" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -2766,7 +2885,7 @@
       <c r="A261">
         <v>259</v>
       </c>
-      <c r="B261" s="8">
+      <c r="B261" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2774,7 +2893,7 @@
       <c r="A262">
         <v>260</v>
       </c>
-      <c r="B262" s="8">
+      <c r="B262" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2782,7 +2901,7 @@
       <c r="A263">
         <v>261</v>
       </c>
-      <c r="B263" s="8">
+      <c r="B263" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2790,7 +2909,7 @@
       <c r="A264">
         <v>262</v>
       </c>
-      <c r="B264" s="8">
+      <c r="B264" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2798,7 +2917,7 @@
       <c r="A265">
         <v>263</v>
       </c>
-      <c r="B265" s="8">
+      <c r="B265" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2806,7 +2925,7 @@
       <c r="A266">
         <v>264</v>
       </c>
-      <c r="B266" s="8">
+      <c r="B266" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2814,7 +2933,7 @@
       <c r="A267">
         <v>265</v>
       </c>
-      <c r="B267" s="8">
+      <c r="B267" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2822,7 +2941,7 @@
       <c r="A268">
         <v>266</v>
       </c>
-      <c r="B268" s="8">
+      <c r="B268" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2830,7 +2949,7 @@
       <c r="A269">
         <v>267</v>
       </c>
-      <c r="B269" s="8">
+      <c r="B269" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2838,7 +2957,7 @@
       <c r="A270">
         <v>268</v>
       </c>
-      <c r="B270" s="8">
+      <c r="B270" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2846,7 +2965,7 @@
       <c r="A271">
         <v>269</v>
       </c>
-      <c r="B271" s="8">
+      <c r="B271" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2854,7 +2973,7 @@
       <c r="A272">
         <v>270</v>
       </c>
-      <c r="B272" s="8">
+      <c r="B272" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2862,7 +2981,7 @@
       <c r="A273">
         <v>271</v>
       </c>
-      <c r="B273" s="8">
+      <c r="B273" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2870,7 +2989,7 @@
       <c r="A274">
         <v>272</v>
       </c>
-      <c r="B274" s="8">
+      <c r="B274" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2878,7 +2997,7 @@
       <c r="A275">
         <v>273</v>
       </c>
-      <c r="B275" s="8">
+      <c r="B275" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2886,7 +3005,7 @@
       <c r="A276">
         <v>274</v>
       </c>
-      <c r="B276" s="8">
+      <c r="B276" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2894,7 +3013,7 @@
       <c r="A277">
         <v>275</v>
       </c>
-      <c r="B277" s="8">
+      <c r="B277" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2902,7 +3021,7 @@
       <c r="A278">
         <v>276</v>
       </c>
-      <c r="B278" s="8">
+      <c r="B278" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2910,7 +3029,7 @@
       <c r="A279">
         <v>277</v>
       </c>
-      <c r="B279" s="8">
+      <c r="B279" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2918,7 +3037,7 @@
       <c r="A280">
         <v>278</v>
       </c>
-      <c r="B280" s="8">
+      <c r="B280" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2926,7 +3045,7 @@
       <c r="A281">
         <v>279</v>
       </c>
-      <c r="B281" s="8">
+      <c r="B281" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2934,7 +3053,7 @@
       <c r="A282">
         <v>280</v>
       </c>
-      <c r="B282" s="8">
+      <c r="B282" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2942,7 +3061,7 @@
       <c r="A283">
         <v>281</v>
       </c>
-      <c r="B283" s="8">
+      <c r="B283" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2950,7 +3069,7 @@
       <c r="A284">
         <v>282</v>
       </c>
-      <c r="B284" s="8">
+      <c r="B284" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2958,7 +3077,7 @@
       <c r="A285">
         <v>283</v>
       </c>
-      <c r="B285" s="8">
+      <c r="B285" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2966,7 +3085,7 @@
       <c r="A286">
         <v>284</v>
       </c>
-      <c r="B286" s="8">
+      <c r="B286" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2974,7 +3093,7 @@
       <c r="A287">
         <v>285</v>
       </c>
-      <c r="B287" s="8">
+      <c r="B287" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -2982,7 +3101,7 @@
       <c r="A288">
         <v>286</v>
       </c>
-      <c r="B288" s="8">
+      <c r="B288" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -2990,7 +3109,7 @@
       <c r="A289">
         <v>287</v>
       </c>
-      <c r="B289" s="8">
+      <c r="B289" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -2998,7 +3117,7 @@
       <c r="A290">
         <v>288</v>
       </c>
-      <c r="B290" s="8">
+      <c r="B290" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3006,7 +3125,7 @@
       <c r="A291">
         <v>289</v>
       </c>
-      <c r="B291" s="8">
+      <c r="B291" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3014,7 +3133,7 @@
       <c r="A292">
         <v>290</v>
       </c>
-      <c r="B292" s="8">
+      <c r="B292" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -3022,7 +3141,7 @@
       <c r="A293">
         <v>291</v>
       </c>
-      <c r="B293" s="8">
+      <c r="B293" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3030,7 +3149,7 @@
       <c r="A294">
         <v>292</v>
       </c>
-      <c r="B294" s="8">
+      <c r="B294" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3038,7 +3157,7 @@
       <c r="A295">
         <v>293</v>
       </c>
-      <c r="B295" s="8">
+      <c r="B295" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3046,7 +3165,7 @@
       <c r="A296">
         <v>294</v>
       </c>
-      <c r="B296" s="8">
+      <c r="B296" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3054,7 +3173,7 @@
       <c r="A297">
         <v>295</v>
       </c>
-      <c r="B297" s="8">
+      <c r="B297" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3062,7 +3181,7 @@
       <c r="A298">
         <v>296</v>
       </c>
-      <c r="B298" s="8">
+      <c r="B298" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3070,7 +3189,7 @@
       <c r="A299">
         <v>297</v>
       </c>
-      <c r="B299" s="8">
+      <c r="B299" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -3078,7 +3197,7 @@
       <c r="A300">
         <v>298</v>
       </c>
-      <c r="B300" s="8">
+      <c r="B300" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -3086,7 +3205,7 @@
       <c r="A301">
         <v>299</v>
       </c>
-      <c r="B301" s="8">
+      <c r="B301" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -3094,7 +3213,7 @@
       <c r="A302">
         <v>300</v>
       </c>
-      <c r="B302" s="8">
+      <c r="B302" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -3102,7 +3221,7 @@
       <c r="A303">
         <v>301</v>
       </c>
-      <c r="B303" s="8">
+      <c r="B303" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3110,7 +3229,7 @@
       <c r="A304">
         <v>302</v>
       </c>
-      <c r="B304" s="8">
+      <c r="B304" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3118,7 +3237,7 @@
       <c r="A305">
         <v>303</v>
       </c>
-      <c r="B305" s="8">
+      <c r="B305" s="7">
         <v>47.7</v>
       </c>
     </row>
@@ -3126,7 +3245,7 @@
       <c r="A306">
         <v>304</v>
       </c>
-      <c r="B306" s="8">
+      <c r="B306" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3134,7 +3253,7 @@
       <c r="A307">
         <v>305</v>
       </c>
-      <c r="B307" s="8">
+      <c r="B307" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3142,7 +3261,7 @@
       <c r="A308">
         <v>306</v>
       </c>
-      <c r="B308" s="8">
+      <c r="B308" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3150,7 +3269,7 @@
       <c r="A309">
         <v>307</v>
       </c>
-      <c r="B309" s="8">
+      <c r="B309" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3158,7 +3277,7 @@
       <c r="A310">
         <v>308</v>
       </c>
-      <c r="B310" s="8">
+      <c r="B310" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3166,7 +3285,7 @@
       <c r="A311">
         <v>309</v>
       </c>
-      <c r="B311" s="8">
+      <c r="B311" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3174,7 +3293,7 @@
       <c r="A312">
         <v>310</v>
       </c>
-      <c r="B312" s="8">
+      <c r="B312" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3182,7 +3301,7 @@
       <c r="A313">
         <v>311</v>
       </c>
-      <c r="B313" s="8">
+      <c r="B313" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3190,7 +3309,7 @@
       <c r="A314">
         <v>312</v>
       </c>
-      <c r="B314" s="8">
+      <c r="B314" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3198,7 +3317,7 @@
       <c r="A315">
         <v>313</v>
       </c>
-      <c r="B315" s="8">
+      <c r="B315" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3206,7 +3325,7 @@
       <c r="A316">
         <v>314</v>
       </c>
-      <c r="B316" s="8">
+      <c r="B316" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3214,7 +3333,7 @@
       <c r="A317">
         <v>315</v>
       </c>
-      <c r="B317" s="8">
+      <c r="B317" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3222,7 +3341,7 @@
       <c r="A318">
         <v>316</v>
       </c>
-      <c r="B318" s="8">
+      <c r="B318" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3230,7 +3349,7 @@
       <c r="A319">
         <v>317</v>
       </c>
-      <c r="B319" s="8">
+      <c r="B319" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3238,7 +3357,7 @@
       <c r="A320">
         <v>318</v>
       </c>
-      <c r="B320" s="8">
+      <c r="B320" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3246,7 +3365,7 @@
       <c r="A321">
         <v>319</v>
       </c>
-      <c r="B321" s="8">
+      <c r="B321" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3254,7 +3373,7 @@
       <c r="A322">
         <v>320</v>
       </c>
-      <c r="B322" s="8">
+      <c r="B322" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3262,7 +3381,7 @@
       <c r="A323">
         <v>321</v>
       </c>
-      <c r="B323" s="8">
+      <c r="B323" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3270,7 +3389,7 @@
       <c r="A324">
         <v>322</v>
       </c>
-      <c r="B324" s="8">
+      <c r="B324" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3278,7 +3397,7 @@
       <c r="A325">
         <v>323</v>
       </c>
-      <c r="B325" s="8">
+      <c r="B325" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3286,7 +3405,7 @@
       <c r="A326">
         <v>324</v>
       </c>
-      <c r="B326" s="8">
+      <c r="B326" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3294,7 +3413,7 @@
       <c r="A327">
         <v>325</v>
       </c>
-      <c r="B327" s="8">
+      <c r="B327" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3302,7 +3421,7 @@
       <c r="A328">
         <v>326</v>
       </c>
-      <c r="B328" s="8">
+      <c r="B328" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3310,7 +3429,7 @@
       <c r="A329">
         <v>327</v>
       </c>
-      <c r="B329" s="8">
+      <c r="B329" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3318,7 +3437,7 @@
       <c r="A330">
         <v>328</v>
       </c>
-      <c r="B330" s="8">
+      <c r="B330" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3326,7 +3445,7 @@
       <c r="A331">
         <v>329</v>
       </c>
-      <c r="B331" s="8">
+      <c r="B331" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3334,7 +3453,7 @@
       <c r="A332">
         <v>330</v>
       </c>
-      <c r="B332" s="8">
+      <c r="B332" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3342,7 +3461,7 @@
       <c r="A333">
         <v>331</v>
       </c>
-      <c r="B333" s="8">
+      <c r="B333" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3350,7 +3469,7 @@
       <c r="A334">
         <v>332</v>
       </c>
-      <c r="B334" s="8">
+      <c r="B334" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3358,7 +3477,7 @@
       <c r="A335">
         <v>333</v>
       </c>
-      <c r="B335" s="8">
+      <c r="B335" s="7">
         <v>47.8</v>
       </c>
     </row>
@@ -3366,7 +3485,7 @@
       <c r="A336">
         <v>334</v>
       </c>
-      <c r="B336" s="8">
+      <c r="B336" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3374,7 +3493,7 @@
       <c r="A337">
         <v>335</v>
       </c>
-      <c r="B337" s="8">
+      <c r="B337" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3382,7 +3501,7 @@
       <c r="A338">
         <v>336</v>
       </c>
-      <c r="B338" s="8">
+      <c r="B338" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3390,7 +3509,7 @@
       <c r="A339">
         <v>337</v>
       </c>
-      <c r="B339" s="8">
+      <c r="B339" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3398,7 +3517,7 @@
       <c r="A340">
         <v>338</v>
       </c>
-      <c r="B340" s="8">
+      <c r="B340" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3406,7 +3525,7 @@
       <c r="A341">
         <v>339</v>
       </c>
-      <c r="B341" s="8">
+      <c r="B341" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3414,7 +3533,7 @@
       <c r="A342">
         <v>340</v>
       </c>
-      <c r="B342" s="8">
+      <c r="B342" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3422,7 +3541,7 @@
       <c r="A343">
         <v>341</v>
       </c>
-      <c r="B343" s="8">
+      <c r="B343" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3430,7 +3549,7 @@
       <c r="A344">
         <v>342</v>
       </c>
-      <c r="B344" s="8">
+      <c r="B344" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3438,7 +3557,7 @@
       <c r="A345">
         <v>343</v>
       </c>
-      <c r="B345" s="8">
+      <c r="B345" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3446,7 +3565,7 @@
       <c r="A346">
         <v>344</v>
       </c>
-      <c r="B346" s="8">
+      <c r="B346" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3454,7 +3573,7 @@
       <c r="A347">
         <v>345</v>
       </c>
-      <c r="B347" s="8">
+      <c r="B347" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3462,7 +3581,7 @@
       <c r="A348">
         <v>346</v>
       </c>
-      <c r="B348" s="8">
+      <c r="B348" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3470,7 +3589,7 @@
       <c r="A349">
         <v>347</v>
       </c>
-      <c r="B349" s="8">
+      <c r="B349" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3478,7 +3597,7 @@
       <c r="A350">
         <v>348</v>
       </c>
-      <c r="B350" s="8">
+      <c r="B350" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3486,7 +3605,7 @@
       <c r="A351">
         <v>349</v>
       </c>
-      <c r="B351" s="8">
+      <c r="B351" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3494,7 +3613,7 @@
       <c r="A352">
         <v>350</v>
       </c>
-      <c r="B352" s="8">
+      <c r="B352" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3502,7 +3621,7 @@
       <c r="A353">
         <v>351</v>
       </c>
-      <c r="B353" s="8">
+      <c r="B353" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3510,7 +3629,7 @@
       <c r="A354">
         <v>352</v>
       </c>
-      <c r="B354" s="8">
+      <c r="B354" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3518,7 +3637,7 @@
       <c r="A355">
         <v>353</v>
       </c>
-      <c r="B355" s="8">
+      <c r="B355" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3526,7 +3645,7 @@
       <c r="A356">
         <v>354</v>
       </c>
-      <c r="B356" s="8">
+      <c r="B356" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3534,7 +3653,7 @@
       <c r="A357">
         <v>355</v>
       </c>
-      <c r="B357" s="8">
+      <c r="B357" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3542,7 +3661,7 @@
       <c r="A358">
         <v>356</v>
       </c>
-      <c r="B358" s="8">
+      <c r="B358" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3550,7 +3669,7 @@
       <c r="A359">
         <v>357</v>
       </c>
-      <c r="B359" s="8">
+      <c r="B359" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3558,7 +3677,7 @@
       <c r="A360">
         <v>358</v>
       </c>
-      <c r="B360" s="8">
+      <c r="B360" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3566,7 +3685,7 @@
       <c r="A361">
         <v>359</v>
       </c>
-      <c r="B361" s="8">
+      <c r="B361" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3574,7 +3693,7 @@
       <c r="A362">
         <v>360</v>
       </c>
-      <c r="B362" s="8">
+      <c r="B362" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3582,7 +3701,7 @@
       <c r="A363">
         <v>361</v>
       </c>
-      <c r="B363" s="8">
+      <c r="B363" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3590,7 +3709,7 @@
       <c r="A364">
         <v>362</v>
       </c>
-      <c r="B364" s="8">
+      <c r="B364" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3598,7 +3717,7 @@
       <c r="A365">
         <v>363</v>
       </c>
-      <c r="B365" s="8">
+      <c r="B365" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3606,7 +3725,7 @@
       <c r="A366">
         <v>364</v>
       </c>
-      <c r="B366" s="8">
+      <c r="B366" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3614,7 +3733,7 @@
       <c r="A367">
         <v>365</v>
       </c>
-      <c r="B367" s="8">
+      <c r="B367" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3622,7 +3741,7 @@
       <c r="A368">
         <v>366</v>
       </c>
-      <c r="B368" s="8">
+      <c r="B368" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3630,7 +3749,7 @@
       <c r="A369">
         <v>367</v>
       </c>
-      <c r="B369" s="8">
+      <c r="B369" s="7">
         <v>47.9</v>
       </c>
     </row>
@@ -3638,7 +3757,7 @@
       <c r="A370">
         <v>368</v>
       </c>
-      <c r="B370" s="8">
+      <c r="B370" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3646,7 +3765,7 @@
       <c r="A371">
         <v>369</v>
       </c>
-      <c r="B371" s="8">
+      <c r="B371" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3654,7 +3773,7 @@
       <c r="A372">
         <v>370</v>
       </c>
-      <c r="B372" s="8">
+      <c r="B372" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3662,7 +3781,7 @@
       <c r="A373">
         <v>371</v>
       </c>
-      <c r="B373" s="8">
+      <c r="B373" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3670,7 +3789,7 @@
       <c r="A374">
         <v>372</v>
       </c>
-      <c r="B374" s="8">
+      <c r="B374" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3678,7 +3797,7 @@
       <c r="A375">
         <v>373</v>
       </c>
-      <c r="B375" s="8">
+      <c r="B375" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3686,7 +3805,7 @@
       <c r="A376">
         <v>374</v>
       </c>
-      <c r="B376" s="8">
+      <c r="B376" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3694,7 +3813,7 @@
       <c r="A377">
         <v>375</v>
       </c>
-      <c r="B377" s="8">
+      <c r="B377" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3702,7 +3821,7 @@
       <c r="A378">
         <v>376</v>
       </c>
-      <c r="B378" s="8">
+      <c r="B378" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3710,7 +3829,7 @@
       <c r="A379">
         <v>377</v>
       </c>
-      <c r="B379" s="8">
+      <c r="B379" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3718,7 +3837,7 @@
       <c r="A380">
         <v>378</v>
       </c>
-      <c r="B380" s="8">
+      <c r="B380" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3726,7 +3845,7 @@
       <c r="A381">
         <v>379</v>
       </c>
-      <c r="B381" s="8">
+      <c r="B381" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3734,7 +3853,7 @@
       <c r="A382">
         <v>380</v>
       </c>
-      <c r="B382" s="8">
+      <c r="B382" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3742,7 +3861,7 @@
       <c r="A383">
         <v>381</v>
       </c>
-      <c r="B383" s="8">
+      <c r="B383" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3750,7 +3869,7 @@
       <c r="A384">
         <v>382</v>
       </c>
-      <c r="B384" s="8">
+      <c r="B384" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3758,7 +3877,7 @@
       <c r="A385">
         <v>383</v>
       </c>
-      <c r="B385" s="8">
+      <c r="B385" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3766,7 +3885,7 @@
       <c r="A386">
         <v>384</v>
       </c>
-      <c r="B386" s="8">
+      <c r="B386" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3774,7 +3893,7 @@
       <c r="A387">
         <v>385</v>
       </c>
-      <c r="B387" s="8">
+      <c r="B387" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3782,7 +3901,7 @@
       <c r="A388">
         <v>386</v>
       </c>
-      <c r="B388" s="8">
+      <c r="B388" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3790,7 +3909,7 @@
       <c r="A389">
         <v>387</v>
       </c>
-      <c r="B389" s="8">
+      <c r="B389" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3798,7 +3917,7 @@
       <c r="A390">
         <v>388</v>
       </c>
-      <c r="B390" s="8">
+      <c r="B390" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3806,7 +3925,7 @@
       <c r="A391">
         <v>389</v>
       </c>
-      <c r="B391" s="8">
+      <c r="B391" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3814,7 +3933,7 @@
       <c r="A392">
         <v>390</v>
       </c>
-      <c r="B392" s="8">
+      <c r="B392" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3822,7 +3941,7 @@
       <c r="A393">
         <v>391</v>
       </c>
-      <c r="B393" s="8">
+      <c r="B393" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3830,7 +3949,7 @@
       <c r="A394">
         <v>392</v>
       </c>
-      <c r="B394" s="8">
+      <c r="B394" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3838,7 +3957,7 @@
       <c r="A395">
         <v>393</v>
       </c>
-      <c r="B395" s="8">
+      <c r="B395" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3846,7 +3965,7 @@
       <c r="A396">
         <v>394</v>
       </c>
-      <c r="B396" s="8">
+      <c r="B396" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3854,7 +3973,7 @@
       <c r="A397">
         <v>395</v>
       </c>
-      <c r="B397" s="8">
+      <c r="B397" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3862,7 +3981,7 @@
       <c r="A398">
         <v>396</v>
       </c>
-      <c r="B398" s="8">
+      <c r="B398" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3870,7 +3989,7 @@
       <c r="A399">
         <v>397</v>
       </c>
-      <c r="B399" s="8">
+      <c r="B399" s="7">
         <v>48</v>
       </c>
     </row>
@@ -3878,7 +3997,7 @@
       <c r="A400">
         <v>398</v>
       </c>
-      <c r="B400" s="8">
+      <c r="B400" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3886,7 +4005,7 @@
       <c r="A401">
         <v>399</v>
       </c>
-      <c r="B401" s="8">
+      <c r="B401" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3894,7 +4013,7 @@
       <c r="A402">
         <v>400</v>
       </c>
-      <c r="B402" s="8">
+      <c r="B402" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3902,7 +4021,7 @@
       <c r="A403">
         <v>401</v>
       </c>
-      <c r="B403" s="8">
+      <c r="B403" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3910,7 +4029,7 @@
       <c r="A404">
         <v>402</v>
       </c>
-      <c r="B404" s="8">
+      <c r="B404" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3918,7 +4037,7 @@
       <c r="A405">
         <v>403</v>
       </c>
-      <c r="B405" s="8">
+      <c r="B405" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3926,7 +4045,7 @@
       <c r="A406">
         <v>404</v>
       </c>
-      <c r="B406" s="8">
+      <c r="B406" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3934,7 +4053,7 @@
       <c r="A407">
         <v>405</v>
       </c>
-      <c r="B407" s="8">
+      <c r="B407" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3942,7 +4061,7 @@
       <c r="A408">
         <v>406</v>
       </c>
-      <c r="B408" s="8">
+      <c r="B408" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3950,7 +4069,7 @@
       <c r="A409">
         <v>407</v>
       </c>
-      <c r="B409" s="8">
+      <c r="B409" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3958,7 +4077,7 @@
       <c r="A410">
         <v>408</v>
       </c>
-      <c r="B410" s="8">
+      <c r="B410" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3966,7 +4085,7 @@
       <c r="A411">
         <v>409</v>
       </c>
-      <c r="B411" s="8">
+      <c r="B411" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3974,7 +4093,7 @@
       <c r="A412">
         <v>410</v>
       </c>
-      <c r="B412" s="8">
+      <c r="B412" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -3982,7 +4101,7 @@
       <c r="A413">
         <v>411</v>
       </c>
-      <c r="B413" s="8">
+      <c r="B413" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -3990,7 +4109,7 @@
       <c r="A414">
         <v>412</v>
       </c>
-      <c r="B414" s="8">
+      <c r="B414" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -3998,7 +4117,7 @@
       <c r="A415">
         <v>413</v>
       </c>
-      <c r="B415" s="8">
+      <c r="B415" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4006,7 +4125,7 @@
       <c r="A416">
         <v>414</v>
       </c>
-      <c r="B416" s="8">
+      <c r="B416" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4014,7 +4133,7 @@
       <c r="A417">
         <v>415</v>
       </c>
-      <c r="B417" s="8">
+      <c r="B417" s="7">
         <v>48.1</v>
       </c>
     </row>
@@ -4022,7 +4141,7 @@
       <c r="A418">
         <v>416</v>
       </c>
-      <c r="B418" s="8">
+      <c r="B418" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4030,7 +4149,7 @@
       <c r="A419">
         <v>417</v>
       </c>
-      <c r="B419" s="8">
+      <c r="B419" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4038,7 +4157,7 @@
       <c r="A420">
         <v>418</v>
       </c>
-      <c r="B420" s="8">
+      <c r="B420" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4046,7 +4165,7 @@
       <c r="A421">
         <v>419</v>
       </c>
-      <c r="B421" s="8">
+      <c r="B421" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4054,7 +4173,7 @@
       <c r="A422">
         <v>420</v>
       </c>
-      <c r="B422" s="8">
+      <c r="B422" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4062,7 +4181,7 @@
       <c r="A423">
         <v>421</v>
       </c>
-      <c r="B423" s="8">
+      <c r="B423" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4070,7 +4189,7 @@
       <c r="A424">
         <v>422</v>
       </c>
-      <c r="B424" s="8">
+      <c r="B424" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4078,7 +4197,7 @@
       <c r="A425">
         <v>423</v>
       </c>
-      <c r="B425" s="8">
+      <c r="B425" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4086,7 +4205,7 @@
       <c r="A426">
         <v>424</v>
       </c>
-      <c r="B426" s="8">
+      <c r="B426" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4094,7 +4213,7 @@
       <c r="A427">
         <v>425</v>
       </c>
-      <c r="B427" s="8">
+      <c r="B427" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4102,7 +4221,7 @@
       <c r="A428">
         <v>426</v>
       </c>
-      <c r="B428" s="8">
+      <c r="B428" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4110,7 +4229,7 @@
       <c r="A429">
         <v>427</v>
       </c>
-      <c r="B429" s="8">
+      <c r="B429" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4118,7 +4237,7 @@
       <c r="A430">
         <v>428</v>
       </c>
-      <c r="B430" s="8">
+      <c r="B430" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4126,7 +4245,7 @@
       <c r="A431">
         <v>429</v>
       </c>
-      <c r="B431" s="8">
+      <c r="B431" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4134,7 +4253,7 @@
       <c r="A432">
         <v>430</v>
       </c>
-      <c r="B432" s="8">
+      <c r="B432" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4142,7 +4261,7 @@
       <c r="A433">
         <v>431</v>
       </c>
-      <c r="B433" s="8">
+      <c r="B433" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4150,7 +4269,7 @@
       <c r="A434">
         <v>432</v>
       </c>
-      <c r="B434" s="8">
+      <c r="B434" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4158,7 +4277,7 @@
       <c r="A435">
         <v>433</v>
       </c>
-      <c r="B435" s="8">
+      <c r="B435" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4166,7 +4285,7 @@
       <c r="A436">
         <v>434</v>
       </c>
-      <c r="B436" s="8">
+      <c r="B436" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4174,7 +4293,7 @@
       <c r="A437">
         <v>435</v>
       </c>
-      <c r="B437" s="8">
+      <c r="B437" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4182,7 +4301,7 @@
       <c r="A438">
         <v>436</v>
       </c>
-      <c r="B438" s="8">
+      <c r="B438" s="7">
         <v>48.2</v>
       </c>
     </row>
@@ -4190,7 +4309,7 @@
       <c r="A439">
         <v>437</v>
       </c>
-      <c r="B439" s="8">
+      <c r="B439" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4198,7 +4317,7 @@
       <c r="A440">
         <v>438</v>
       </c>
-      <c r="B440" s="8">
+      <c r="B440" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4206,7 +4325,7 @@
       <c r="A441">
         <v>439</v>
       </c>
-      <c r="B441" s="8">
+      <c r="B441" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4214,7 +4333,7 @@
       <c r="A442">
         <v>440</v>
       </c>
-      <c r="B442" s="8">
+      <c r="B442" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4222,7 +4341,7 @@
       <c r="A443">
         <v>441</v>
       </c>
-      <c r="B443" s="8">
+      <c r="B443" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4230,7 +4349,7 @@
       <c r="A444">
         <v>442</v>
       </c>
-      <c r="B444" s="8">
+      <c r="B444" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4238,7 +4357,7 @@
       <c r="A445">
         <v>443</v>
       </c>
-      <c r="B445" s="8">
+      <c r="B445" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4246,7 +4365,7 @@
       <c r="A446">
         <v>444</v>
       </c>
-      <c r="B446" s="8">
+      <c r="B446" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4254,7 +4373,7 @@
       <c r="A447">
         <v>445</v>
       </c>
-      <c r="B447" s="8">
+      <c r="B447" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4262,7 +4381,7 @@
       <c r="A448">
         <v>446</v>
       </c>
-      <c r="B448" s="8">
+      <c r="B448" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4270,7 +4389,7 @@
       <c r="A449">
         <v>447</v>
       </c>
-      <c r="B449" s="8">
+      <c r="B449" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4278,7 +4397,7 @@
       <c r="A450">
         <v>448</v>
       </c>
-      <c r="B450" s="8">
+      <c r="B450" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4286,7 +4405,7 @@
       <c r="A451">
         <v>449</v>
       </c>
-      <c r="B451" s="8">
+      <c r="B451" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4294,7 +4413,7 @@
       <c r="A452">
         <v>450</v>
       </c>
-      <c r="B452" s="8">
+      <c r="B452" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4302,7 +4421,7 @@
       <c r="A453">
         <v>451</v>
       </c>
-      <c r="B453" s="8">
+      <c r="B453" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4310,7 +4429,7 @@
       <c r="A454">
         <v>452</v>
       </c>
-      <c r="B454" s="8">
+      <c r="B454" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4318,7 +4437,7 @@
       <c r="A455">
         <v>453</v>
       </c>
-      <c r="B455" s="8">
+      <c r="B455" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4326,7 +4445,7 @@
       <c r="A456">
         <v>454</v>
       </c>
-      <c r="B456" s="8">
+      <c r="B456" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4334,7 +4453,7 @@
       <c r="A457">
         <v>455</v>
       </c>
-      <c r="B457" s="8">
+      <c r="B457" s="7">
         <v>48.3</v>
       </c>
     </row>
@@ -4342,7 +4461,7 @@
       <c r="A458">
         <v>456</v>
       </c>
-      <c r="B458" s="8">
+      <c r="B458" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4350,7 +4469,7 @@
       <c r="A459">
         <v>457</v>
       </c>
-      <c r="B459" s="8">
+      <c r="B459" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4358,7 +4477,7 @@
       <c r="A460">
         <v>458</v>
       </c>
-      <c r="B460" s="8">
+      <c r="B460" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4366,7 +4485,7 @@
       <c r="A461">
         <v>459</v>
       </c>
-      <c r="B461" s="8">
+      <c r="B461" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4374,7 +4493,7 @@
       <c r="A462">
         <v>460</v>
       </c>
-      <c r="B462" s="8">
+      <c r="B462" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4382,7 +4501,7 @@
       <c r="A463">
         <v>461</v>
       </c>
-      <c r="B463" s="8">
+      <c r="B463" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4390,7 +4509,7 @@
       <c r="A464">
         <v>462</v>
       </c>
-      <c r="B464" s="8">
+      <c r="B464" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4398,7 +4517,7 @@
       <c r="A465">
         <v>463</v>
       </c>
-      <c r="B465" s="8">
+      <c r="B465" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4406,7 +4525,7 @@
       <c r="A466">
         <v>464</v>
       </c>
-      <c r="B466" s="8">
+      <c r="B466" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4414,7 +4533,7 @@
       <c r="A467">
         <v>465</v>
       </c>
-      <c r="B467" s="8">
+      <c r="B467" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4422,7 +4541,7 @@
       <c r="A468">
         <v>466</v>
       </c>
-      <c r="B468" s="8">
+      <c r="B468" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4430,7 +4549,7 @@
       <c r="A469">
         <v>467</v>
       </c>
-      <c r="B469" s="8">
+      <c r="B469" s="7">
         <v>48.4</v>
       </c>
     </row>
@@ -4438,7 +4557,7 @@
       <c r="A470">
         <v>468</v>
       </c>
-      <c r="B470" s="8">
+      <c r="B470" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4446,7 +4565,7 @@
       <c r="A471">
         <v>469</v>
       </c>
-      <c r="B471" s="8">
+      <c r="B471" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4454,7 +4573,7 @@
       <c r="A472">
         <v>470</v>
       </c>
-      <c r="B472" s="8">
+      <c r="B472" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4462,7 +4581,7 @@
       <c r="A473">
         <v>471</v>
       </c>
-      <c r="B473" s="8">
+      <c r="B473" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4470,7 +4589,7 @@
       <c r="A474">
         <v>472</v>
       </c>
-      <c r="B474" s="8">
+      <c r="B474" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4478,7 +4597,7 @@
       <c r="A475">
         <v>473</v>
       </c>
-      <c r="B475" s="8">
+      <c r="B475" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4486,7 +4605,7 @@
       <c r="A476">
         <v>474</v>
       </c>
-      <c r="B476" s="8">
+      <c r="B476" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4494,7 +4613,7 @@
       <c r="A477">
         <v>475</v>
       </c>
-      <c r="B477" s="8">
+      <c r="B477" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4502,7 +4621,7 @@
       <c r="A478">
         <v>476</v>
       </c>
-      <c r="B478" s="8">
+      <c r="B478" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4510,7 +4629,7 @@
       <c r="A479">
         <v>477</v>
       </c>
-      <c r="B479" s="8">
+      <c r="B479" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4518,7 +4637,7 @@
       <c r="A480">
         <v>478</v>
       </c>
-      <c r="B480" s="8">
+      <c r="B480" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4526,7 +4645,7 @@
       <c r="A481">
         <v>479</v>
       </c>
-      <c r="B481" s="8">
+      <c r="B481" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4534,7 +4653,7 @@
       <c r="A482">
         <v>480</v>
       </c>
-      <c r="B482" s="8">
+      <c r="B482" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4542,7 +4661,7 @@
       <c r="A483">
         <v>481</v>
       </c>
-      <c r="B483" s="8">
+      <c r="B483" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4550,7 +4669,7 @@
       <c r="A484">
         <v>482</v>
       </c>
-      <c r="B484" s="8">
+      <c r="B484" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4558,7 +4677,7 @@
       <c r="A485">
         <v>483</v>
       </c>
-      <c r="B485" s="8">
+      <c r="B485" s="7">
         <v>48.5</v>
       </c>
     </row>
@@ -4566,7 +4685,7 @@
       <c r="A486">
         <v>484</v>
       </c>
-      <c r="B486" s="8">
+      <c r="B486" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4574,7 +4693,7 @@
       <c r="A487">
         <v>485</v>
       </c>
-      <c r="B487" s="8">
+      <c r="B487" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4582,7 +4701,7 @@
       <c r="A488">
         <v>486</v>
       </c>
-      <c r="B488" s="8">
+      <c r="B488" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4590,7 +4709,7 @@
       <c r="A489">
         <v>487</v>
       </c>
-      <c r="B489" s="8">
+      <c r="B489" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4598,7 +4717,7 @@
       <c r="A490">
         <v>488</v>
       </c>
-      <c r="B490" s="8">
+      <c r="B490" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4606,7 +4725,7 @@
       <c r="A491">
         <v>489</v>
       </c>
-      <c r="B491" s="8">
+      <c r="B491" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4614,7 +4733,7 @@
       <c r="A492">
         <v>490</v>
       </c>
-      <c r="B492" s="8">
+      <c r="B492" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4622,7 +4741,7 @@
       <c r="A493">
         <v>491</v>
       </c>
-      <c r="B493" s="8">
+      <c r="B493" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4630,7 +4749,7 @@
       <c r="A494">
         <v>492</v>
       </c>
-      <c r="B494" s="8">
+      <c r="B494" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4638,7 +4757,7 @@
       <c r="A495">
         <v>493</v>
       </c>
-      <c r="B495" s="8">
+      <c r="B495" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4646,7 +4765,7 @@
       <c r="A496">
         <v>494</v>
       </c>
-      <c r="B496" s="8">
+      <c r="B496" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4654,7 +4773,7 @@
       <c r="A497">
         <v>495</v>
       </c>
-      <c r="B497" s="8">
+      <c r="B497" s="7">
         <v>48.6</v>
       </c>
     </row>
@@ -4662,7 +4781,7 @@
       <c r="A498">
         <v>496</v>
       </c>
-      <c r="B498" s="8">
+      <c r="B498" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4670,7 +4789,7 @@
       <c r="A499">
         <v>497</v>
       </c>
-      <c r="B499" s="8">
+      <c r="B499" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4678,7 +4797,7 @@
       <c r="A500">
         <v>498</v>
       </c>
-      <c r="B500" s="8">
+      <c r="B500" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4686,7 +4805,7 @@
       <c r="A501">
         <v>499</v>
       </c>
-      <c r="B501" s="8">
+      <c r="B501" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4694,7 +4813,7 @@
       <c r="A502">
         <v>500</v>
       </c>
-      <c r="B502" s="8">
+      <c r="B502" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4702,7 +4821,7 @@
       <c r="A503">
         <v>501</v>
       </c>
-      <c r="B503" s="8">
+      <c r="B503" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4710,7 +4829,7 @@
       <c r="A504">
         <v>502</v>
       </c>
-      <c r="B504" s="8">
+      <c r="B504" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4718,7 +4837,7 @@
       <c r="A505">
         <v>503</v>
       </c>
-      <c r="B505" s="8">
+      <c r="B505" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4726,7 +4845,7 @@
       <c r="A506">
         <v>504</v>
       </c>
-      <c r="B506" s="8">
+      <c r="B506" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4734,7 +4853,7 @@
       <c r="A507">
         <v>505</v>
       </c>
-      <c r="B507" s="8">
+      <c r="B507" s="7">
         <v>48.7</v>
       </c>
     </row>
@@ -4742,7 +4861,7 @@
       <c r="A508">
         <v>506</v>
       </c>
-      <c r="B508" s="8">
+      <c r="B508" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4750,7 +4869,7 @@
       <c r="A509">
         <v>507</v>
       </c>
-      <c r="B509" s="8">
+      <c r="B509" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4758,7 +4877,7 @@
       <c r="A510">
         <v>508</v>
       </c>
-      <c r="B510" s="8">
+      <c r="B510" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4766,7 +4885,7 @@
       <c r="A511">
         <v>509</v>
       </c>
-      <c r="B511" s="8">
+      <c r="B511" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4774,7 +4893,7 @@
       <c r="A512">
         <v>510</v>
       </c>
-      <c r="B512" s="8">
+      <c r="B512" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4782,7 +4901,7 @@
       <c r="A513">
         <v>511</v>
       </c>
-      <c r="B513" s="8">
+      <c r="B513" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4790,7 +4909,7 @@
       <c r="A514">
         <v>512</v>
       </c>
-      <c r="B514" s="8">
+      <c r="B514" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4798,7 +4917,7 @@
       <c r="A515">
         <v>513</v>
       </c>
-      <c r="B515" s="8">
+      <c r="B515" s="7">
         <v>48.8</v>
       </c>
     </row>
@@ -4806,7 +4925,7 @@
       <c r="A516">
         <v>514</v>
       </c>
-      <c r="B516" s="8">
+      <c r="B516" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -4814,7 +4933,7 @@
       <c r="A517">
         <v>515</v>
       </c>
-      <c r="B517" s="8">
+      <c r="B517" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -4822,7 +4941,7 @@
       <c r="A518">
         <v>516</v>
       </c>
-      <c r="B518" s="8">
+      <c r="B518" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -4830,7 +4949,7 @@
       <c r="A519">
         <v>517</v>
       </c>
-      <c r="B519" s="8">
+      <c r="B519" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -4838,7 +4957,7 @@
       <c r="A520">
         <v>518</v>
       </c>
-      <c r="B520" s="8">
+      <c r="B520" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -4846,7 +4965,7 @@
       <c r="A521">
         <v>519</v>
       </c>
-      <c r="B521" s="8">
+      <c r="B521" s="7">
         <v>48.9</v>
       </c>
     </row>
@@ -4854,7 +4973,7 @@
       <c r="A522">
         <v>520</v>
       </c>
-      <c r="B522" s="8">
+      <c r="B522" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4862,7 +4981,7 @@
       <c r="A523">
         <v>521</v>
       </c>
-      <c r="B523" s="8">
+      <c r="B523" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4870,7 +4989,7 @@
       <c r="A524">
         <v>522</v>
       </c>
-      <c r="B524" s="8">
+      <c r="B524" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4878,7 +4997,7 @@
       <c r="A525">
         <v>523</v>
       </c>
-      <c r="B525" s="8">
+      <c r="B525" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4886,7 +5005,7 @@
       <c r="A526">
         <v>524</v>
       </c>
-      <c r="B526" s="8">
+      <c r="B526" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4894,7 +5013,7 @@
       <c r="A527">
         <v>525</v>
       </c>
-      <c r="B527" s="8">
+      <c r="B527" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4902,7 +5021,7 @@
       <c r="A528">
         <v>526</v>
       </c>
-      <c r="B528" s="8">
+      <c r="B528" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4910,7 +5029,7 @@
       <c r="A529">
         <v>527</v>
       </c>
-      <c r="B529" s="8">
+      <c r="B529" s="7">
         <v>49</v>
       </c>
     </row>
@@ -4918,7 +5037,7 @@
       <c r="A530">
         <v>528</v>
       </c>
-      <c r="B530" s="8">
+      <c r="B530" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -4926,7 +5045,7 @@
       <c r="A531">
         <v>529</v>
       </c>
-      <c r="B531" s="8">
+      <c r="B531" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -4934,7 +5053,7 @@
       <c r="A532">
         <v>530</v>
       </c>
-      <c r="B532" s="8">
+      <c r="B532" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -4942,7 +5061,7 @@
       <c r="A533">
         <v>531</v>
       </c>
-      <c r="B533" s="8">
+      <c r="B533" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -4950,7 +5069,7 @@
       <c r="A534">
         <v>532</v>
       </c>
-      <c r="B534" s="8">
+      <c r="B534" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -4958,7 +5077,7 @@
       <c r="A535">
         <v>533</v>
       </c>
-      <c r="B535" s="8">
+      <c r="B535" s="7">
         <v>49.1</v>
       </c>
     </row>
@@ -4966,7 +5085,7 @@
       <c r="A536">
         <v>534</v>
       </c>
-      <c r="B536" s="8">
+      <c r="B536" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -4974,7 +5093,7 @@
       <c r="A537">
         <v>535</v>
       </c>
-      <c r="B537" s="8">
+      <c r="B537" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -4982,7 +5101,7 @@
       <c r="A538">
         <v>536</v>
       </c>
-      <c r="B538" s="8">
+      <c r="B538" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -4990,7 +5109,7 @@
       <c r="A539">
         <v>537</v>
       </c>
-      <c r="B539" s="8">
+      <c r="B539" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -4998,7 +5117,7 @@
       <c r="A540">
         <v>538</v>
       </c>
-      <c r="B540" s="8">
+      <c r="B540" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5006,7 +5125,7 @@
       <c r="A541">
         <v>539</v>
       </c>
-      <c r="B541" s="8">
+      <c r="B541" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5014,7 +5133,7 @@
       <c r="A542">
         <v>540</v>
       </c>
-      <c r="B542" s="8">
+      <c r="B542" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5022,7 +5141,7 @@
       <c r="A543">
         <v>541</v>
       </c>
-      <c r="B543" s="8">
+      <c r="B543" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5030,7 +5149,7 @@
       <c r="A544">
         <v>542</v>
       </c>
-      <c r="B544" s="8">
+      <c r="B544" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5038,7 +5157,7 @@
       <c r="A545">
         <v>543</v>
       </c>
-      <c r="B545" s="8">
+      <c r="B545" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5046,7 +5165,7 @@
       <c r="A546">
         <v>544</v>
       </c>
-      <c r="B546" s="8">
+      <c r="B546" s="7">
         <v>49.2</v>
       </c>
     </row>
@@ -5054,7 +5173,7 @@
       <c r="A547">
         <v>545</v>
       </c>
-      <c r="B547" s="8">
+      <c r="B547" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -5062,7 +5181,7 @@
       <c r="A548">
         <v>546</v>
       </c>
-      <c r="B548" s="8">
+      <c r="B548" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -5070,7 +5189,7 @@
       <c r="A549">
         <v>547</v>
       </c>
-      <c r="B549" s="8">
+      <c r="B549" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -5078,7 +5197,7 @@
       <c r="A550">
         <v>548</v>
       </c>
-      <c r="B550" s="8">
+      <c r="B550" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -5086,7 +5205,7 @@
       <c r="A551">
         <v>549</v>
       </c>
-      <c r="B551" s="8">
+      <c r="B551" s="7">
         <v>49.3</v>
       </c>
     </row>
@@ -5094,7 +5213,7 @@
       <c r="A552">
         <v>550</v>
       </c>
-      <c r="B552" s="8">
+      <c r="B552" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -5102,7 +5221,7 @@
       <c r="A553">
         <v>551</v>
       </c>
-      <c r="B553" s="8">
+      <c r="B553" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -5110,7 +5229,7 @@
       <c r="A554">
         <v>552</v>
       </c>
-      <c r="B554" s="8">
+      <c r="B554" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -5118,7 +5237,7 @@
       <c r="A555">
         <v>553</v>
       </c>
-      <c r="B555" s="8">
+      <c r="B555" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -5126,7 +5245,7 @@
       <c r="A556">
         <v>554</v>
       </c>
-      <c r="B556" s="8">
+      <c r="B556" s="7">
         <v>49.4</v>
       </c>
     </row>
@@ -5134,7 +5253,7 @@
       <c r="A557">
         <v>555</v>
       </c>
-      <c r="B557" s="8">
+      <c r="B557" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -5142,7 +5261,7 @@
       <c r="A558">
         <v>556</v>
       </c>
-      <c r="B558" s="8">
+      <c r="B558" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -5150,7 +5269,7 @@
       <c r="A559">
         <v>557</v>
       </c>
-      <c r="B559" s="8">
+      <c r="B559" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -5158,7 +5277,7 @@
       <c r="A560">
         <v>558</v>
       </c>
-      <c r="B560" s="8">
+      <c r="B560" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -5166,7 +5285,7 @@
       <c r="A561">
         <v>559</v>
       </c>
-      <c r="B561" s="8">
+      <c r="B561" s="7">
         <v>49.5</v>
       </c>
     </row>
@@ -5174,7 +5293,7 @@
       <c r="A562">
         <v>560</v>
       </c>
-      <c r="B562" s="8">
+      <c r="B562" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5182,7 +5301,7 @@
       <c r="A563">
         <v>561</v>
       </c>
-      <c r="B563" s="8">
+      <c r="B563" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5190,7 +5309,7 @@
       <c r="A564">
         <v>562</v>
       </c>
-      <c r="B564" s="8">
+      <c r="B564" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5198,7 +5317,7 @@
       <c r="A565">
         <v>563</v>
       </c>
-      <c r="B565" s="8">
+      <c r="B565" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5206,7 +5325,7 @@
       <c r="A566">
         <v>564</v>
       </c>
-      <c r="B566" s="8">
+      <c r="B566" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5214,7 +5333,7 @@
       <c r="A567">
         <v>565</v>
       </c>
-      <c r="B567" s="8">
+      <c r="B567" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5222,7 +5341,7 @@
       <c r="A568">
         <v>566</v>
       </c>
-      <c r="B568" s="8">
+      <c r="B568" s="7">
         <v>49.6</v>
       </c>
     </row>
@@ -5230,7 +5349,7 @@
       <c r="A569">
         <v>567</v>
       </c>
-      <c r="B569" s="8">
+      <c r="B569" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -5238,7 +5357,7 @@
       <c r="A570">
         <v>568</v>
       </c>
-      <c r="B570" s="8">
+      <c r="B570" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -5246,7 +5365,7 @@
       <c r="A571">
         <v>569</v>
       </c>
-      <c r="B571" s="8">
+      <c r="B571" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -5254,7 +5373,7 @@
       <c r="A572">
         <v>570</v>
       </c>
-      <c r="B572" s="8">
+      <c r="B572" s="7">
         <v>49.7</v>
       </c>
     </row>
@@ -5262,7 +5381,7 @@
       <c r="A573">
         <v>571</v>
       </c>
-      <c r="B573" s="8">
+      <c r="B573" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -5270,7 +5389,7 @@
       <c r="A574">
         <v>572</v>
       </c>
-      <c r="B574" s="8">
+      <c r="B574" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -5278,7 +5397,7 @@
       <c r="A575">
         <v>573</v>
       </c>
-      <c r="B575" s="8">
+      <c r="B575" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -5286,7 +5405,7 @@
       <c r="A576">
         <v>574</v>
       </c>
-      <c r="B576" s="8">
+      <c r="B576" s="7">
         <v>49.8</v>
       </c>
     </row>
@@ -5294,7 +5413,7 @@
       <c r="A577">
         <v>575</v>
       </c>
-      <c r="B577" s="8">
+      <c r="B577" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -5302,7 +5421,7 @@
       <c r="A578">
         <v>576</v>
       </c>
-      <c r="B578" s="8">
+      <c r="B578" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -5310,7 +5429,7 @@
       <c r="A579">
         <v>577</v>
       </c>
-      <c r="B579" s="8">
+      <c r="B579" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -5318,7 +5437,7 @@
       <c r="A580">
         <v>578</v>
       </c>
-      <c r="B580" s="8">
+      <c r="B580" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -5326,7 +5445,7 @@
       <c r="A581">
         <v>579</v>
       </c>
-      <c r="B581" s="8">
+      <c r="B581" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -5334,7 +5453,7 @@
       <c r="A582">
         <v>580</v>
       </c>
-      <c r="B582" s="8">
+      <c r="B582" s="7">
         <v>49.9</v>
       </c>
     </row>
@@ -5342,7 +5461,7 @@
       <c r="A583">
         <v>581</v>
       </c>
-      <c r="B583" s="8">
+      <c r="B583" s="7">
         <v>50</v>
       </c>
     </row>
@@ -5350,7 +5469,7 @@
       <c r="A584">
         <v>582</v>
       </c>
-      <c r="B584" s="8">
+      <c r="B584" s="7">
         <v>50</v>
       </c>
     </row>
@@ -5358,7 +5477,7 @@
       <c r="A585">
         <v>583</v>
       </c>
-      <c r="B585" s="8">
+      <c r="B585" s="7">
         <v>50</v>
       </c>
     </row>
@@ -5366,7 +5485,7 @@
       <c r="A586">
         <v>584</v>
       </c>
-      <c r="B586" s="8">
+      <c r="B586" s="7">
         <v>50</v>
       </c>
     </row>
@@ -5374,7 +5493,7 @@
       <c r="A587">
         <v>585</v>
       </c>
-      <c r="B587" s="8">
+      <c r="B587" s="7">
         <v>50</v>
       </c>
     </row>
@@ -5382,7 +5501,7 @@
       <c r="A588">
         <v>586</v>
       </c>
-      <c r="B588" s="8">
+      <c r="B588" s="7">
         <v>50</v>
       </c>
     </row>
@@ -5390,7 +5509,7 @@
       <c r="A589">
         <v>587</v>
       </c>
-      <c r="B589" s="8">
+      <c r="B589" s="7">
         <v>50.1</v>
       </c>
     </row>
@@ -5398,7 +5517,7 @@
       <c r="A590">
         <v>588</v>
       </c>
-      <c r="B590" s="8">
+      <c r="B590" s="7">
         <v>50.1</v>
       </c>
     </row>
@@ -5406,7 +5525,7 @@
       <c r="A591">
         <v>589</v>
       </c>
-      <c r="B591" s="8">
+      <c r="B591" s="7">
         <v>50.1</v>
       </c>
     </row>
@@ -5414,7 +5533,7 @@
       <c r="A592">
         <v>590</v>
       </c>
-      <c r="B592" s="8">
+      <c r="B592" s="7">
         <v>50.1</v>
       </c>
     </row>
@@ -5422,7 +5541,7 @@
       <c r="A593">
         <v>591</v>
       </c>
-      <c r="B593" s="8">
+      <c r="B593" s="7">
         <v>50.2</v>
       </c>
     </row>
@@ -5430,7 +5549,7 @@
       <c r="A594">
         <v>592</v>
       </c>
-      <c r="B594" s="8">
+      <c r="B594" s="7">
         <v>50.2</v>
       </c>
     </row>
@@ -5438,7 +5557,7 @@
       <c r="A595">
         <v>593</v>
       </c>
-      <c r="B595" s="8">
+      <c r="B595" s="7">
         <v>50.2</v>
       </c>
     </row>
@@ -5446,7 +5565,7 @@
       <c r="A596">
         <v>594</v>
       </c>
-      <c r="B596" s="8">
+      <c r="B596" s="7">
         <v>50.2</v>
       </c>
     </row>
@@ -5454,7 +5573,7 @@
       <c r="A597">
         <v>595</v>
       </c>
-      <c r="B597" s="8">
+      <c r="B597" s="7">
         <v>50.2</v>
       </c>
     </row>
@@ -5462,7 +5581,7 @@
       <c r="A598">
         <v>596</v>
       </c>
-      <c r="B598" s="8">
+      <c r="B598" s="7">
         <v>50.2</v>
       </c>
     </row>
@@ -5470,7 +5589,7 @@
       <c r="A599">
         <v>597</v>
       </c>
-      <c r="B599" s="8">
+      <c r="B599" s="7">
         <v>50.3</v>
       </c>
     </row>
@@ -5478,7 +5597,7 @@
       <c r="A600">
         <v>598</v>
       </c>
-      <c r="B600" s="8">
+      <c r="B600" s="7">
         <v>50.3</v>
       </c>
     </row>
@@ -5486,7 +5605,7 @@
       <c r="A601">
         <v>599</v>
       </c>
-      <c r="B601" s="8">
+      <c r="B601" s="7">
         <v>50.3</v>
       </c>
     </row>
@@ -5494,7 +5613,7 @@
       <c r="A602">
         <v>600</v>
       </c>
-      <c r="B602" s="8">
+      <c r="B602" s="7">
         <v>50.3</v>
       </c>
     </row>
@@ -5502,7 +5621,7 @@
       <c r="A603">
         <v>601</v>
       </c>
-      <c r="B603" s="8">
+      <c r="B603" s="7">
         <v>50.4</v>
       </c>
     </row>
@@ -5510,7 +5629,7 @@
       <c r="A604">
         <v>602</v>
       </c>
-      <c r="B604" s="8">
+      <c r="B604" s="7">
         <v>50.4</v>
       </c>
     </row>
@@ -5518,7 +5637,7 @@
       <c r="A605">
         <v>603</v>
       </c>
-      <c r="B605" s="8">
+      <c r="B605" s="7">
         <v>50.4</v>
       </c>
     </row>
@@ -5526,7 +5645,7 @@
       <c r="A606">
         <v>604</v>
       </c>
-      <c r="B606" s="8">
+      <c r="B606" s="7">
         <v>50.4</v>
       </c>
     </row>
@@ -5534,7 +5653,7 @@
       <c r="A607">
         <v>605</v>
       </c>
-      <c r="B607" s="8">
+      <c r="B607" s="7">
         <v>50.4</v>
       </c>
     </row>
@@ -5542,7 +5661,7 @@
       <c r="A608">
         <v>606</v>
       </c>
-      <c r="B608" s="8">
+      <c r="B608" s="7">
         <v>50.5</v>
       </c>
     </row>
@@ -5550,7 +5669,7 @@
       <c r="A609">
         <v>607</v>
       </c>
-      <c r="B609" s="8">
+      <c r="B609" s="7">
         <v>50.5</v>
       </c>
     </row>
@@ -5558,7 +5677,7 @@
       <c r="A610">
         <v>608</v>
       </c>
-      <c r="B610" s="8">
+      <c r="B610" s="7">
         <v>50.5</v>
       </c>
     </row>
@@ -5566,7 +5685,7 @@
       <c r="A611">
         <v>609</v>
       </c>
-      <c r="B611" s="8">
+      <c r="B611" s="7">
         <v>50.6</v>
       </c>
     </row>
@@ -5574,7 +5693,7 @@
       <c r="A612">
         <v>610</v>
       </c>
-      <c r="B612" s="8">
+      <c r="B612" s="7">
         <v>50.6</v>
       </c>
     </row>
@@ -5582,7 +5701,7 @@
       <c r="A613">
         <v>611</v>
       </c>
-      <c r="B613" s="8">
+      <c r="B613" s="7">
         <v>50.6</v>
       </c>
     </row>
@@ -5590,7 +5709,7 @@
       <c r="A614">
         <v>612</v>
       </c>
-      <c r="B614" s="8">
+      <c r="B614" s="7">
         <v>50.6</v>
       </c>
     </row>
@@ -5598,7 +5717,7 @@
       <c r="A615">
         <v>613</v>
       </c>
-      <c r="B615" s="8">
+      <c r="B615" s="7">
         <v>50.7</v>
       </c>
     </row>
@@ -5606,7 +5725,7 @@
       <c r="A616">
         <v>614</v>
       </c>
-      <c r="B616" s="8">
+      <c r="B616" s="7">
         <v>50.7</v>
       </c>
     </row>
@@ -5614,7 +5733,7 @@
       <c r="A617">
         <v>615</v>
       </c>
-      <c r="B617" s="8">
+      <c r="B617" s="7">
         <v>50.7</v>
       </c>
     </row>
@@ -5622,7 +5741,7 @@
       <c r="A618">
         <v>616</v>
       </c>
-      <c r="B618" s="8">
+      <c r="B618" s="7">
         <v>50.7</v>
       </c>
     </row>
@@ -5630,7 +5749,7 @@
       <c r="A619">
         <v>617</v>
       </c>
-      <c r="B619" s="8">
+      <c r="B619" s="7">
         <v>50.8</v>
       </c>
     </row>
@@ -5638,7 +5757,7 @@
       <c r="A620">
         <v>618</v>
       </c>
-      <c r="B620" s="8">
+      <c r="B620" s="7">
         <v>50.8</v>
       </c>
     </row>
@@ -5646,7 +5765,7 @@
       <c r="A621">
         <v>619</v>
       </c>
-      <c r="B621" s="8">
+      <c r="B621" s="7">
         <v>50.8</v>
       </c>
     </row>
@@ -5654,7 +5773,7 @@
       <c r="A622">
         <v>620</v>
       </c>
-      <c r="B622" s="8">
+      <c r="B622" s="7">
         <v>50.8</v>
       </c>
     </row>
@@ -5662,7 +5781,7 @@
       <c r="A623">
         <v>621</v>
       </c>
-      <c r="B623" s="8">
+      <c r="B623" s="7">
         <v>50.8</v>
       </c>
     </row>
@@ -5670,7 +5789,7 @@
       <c r="A624">
         <v>622</v>
       </c>
-      <c r="B624" s="8">
+      <c r="B624" s="7">
         <v>50.9</v>
       </c>
     </row>
@@ -5678,7 +5797,7 @@
       <c r="A625">
         <v>623</v>
       </c>
-      <c r="B625" s="8">
+      <c r="B625" s="7">
         <v>50.9</v>
       </c>
     </row>
@@ -5686,7 +5805,7 @@
       <c r="A626">
         <v>624</v>
       </c>
-      <c r="B626" s="8">
+      <c r="B626" s="7">
         <v>50.9</v>
       </c>
     </row>
@@ -5694,7 +5813,7 @@
       <c r="A627">
         <v>625</v>
       </c>
-      <c r="B627" s="8">
+      <c r="B627" s="7">
         <v>50.9</v>
       </c>
     </row>
@@ -5702,7 +5821,7 @@
       <c r="A628">
         <v>626</v>
       </c>
-      <c r="B628" s="8">
+      <c r="B628" s="7">
         <v>51</v>
       </c>
     </row>
@@ -5710,7 +5829,7 @@
       <c r="A629">
         <v>627</v>
       </c>
-      <c r="B629" s="8">
+      <c r="B629" s="7">
         <v>51</v>
       </c>
     </row>
@@ -5718,7 +5837,7 @@
       <c r="A630">
         <v>628</v>
       </c>
-      <c r="B630" s="8">
+      <c r="B630" s="7">
         <v>51</v>
       </c>
     </row>
@@ -5726,7 +5845,7 @@
       <c r="A631">
         <v>629</v>
       </c>
-      <c r="B631" s="8">
+      <c r="B631" s="7">
         <v>51</v>
       </c>
     </row>
@@ -5734,7 +5853,7 @@
       <c r="A632">
         <v>630</v>
       </c>
-      <c r="B632" s="8">
+      <c r="B632" s="7">
         <v>51</v>
       </c>
     </row>
@@ -5742,7 +5861,7 @@
       <c r="A633">
         <v>631</v>
       </c>
-      <c r="B633" s="8">
+      <c r="B633" s="7">
         <v>51.1</v>
       </c>
     </row>
@@ -5750,7 +5869,7 @@
       <c r="A634">
         <v>632</v>
       </c>
-      <c r="B634" s="8">
+      <c r="B634" s="7">
         <v>51.1</v>
       </c>
     </row>
@@ -5758,7 +5877,7 @@
       <c r="A635">
         <v>633</v>
       </c>
-      <c r="B635" s="8">
+      <c r="B635" s="7">
         <v>51.1</v>
       </c>
     </row>
@@ -5766,7 +5885,7 @@
       <c r="A636">
         <v>634</v>
       </c>
-      <c r="B636" s="8">
+      <c r="B636" s="7">
         <v>51.1</v>
       </c>
     </row>
@@ -5774,7 +5893,7 @@
       <c r="A637">
         <v>635</v>
       </c>
-      <c r="B637" s="8">
+      <c r="B637" s="7">
         <v>51.2</v>
       </c>
     </row>
@@ -5782,7 +5901,7 @@
       <c r="A638">
         <v>636</v>
       </c>
-      <c r="B638" s="8">
+      <c r="B638" s="7">
         <v>51.2</v>
       </c>
     </row>
@@ -5790,7 +5909,7 @@
       <c r="A639">
         <v>637</v>
       </c>
-      <c r="B639" s="8">
+      <c r="B639" s="7">
         <v>51.2</v>
       </c>
     </row>
@@ -5798,7 +5917,7 @@
       <c r="A640">
         <v>638</v>
       </c>
-      <c r="B640" s="8">
+      <c r="B640" s="7">
         <v>51.2</v>
       </c>
     </row>
@@ -5806,7 +5925,7 @@
       <c r="A641">
         <v>639</v>
       </c>
-      <c r="B641" s="8">
+      <c r="B641" s="7">
         <v>51.3</v>
       </c>
     </row>
@@ -5814,7 +5933,7 @@
       <c r="A642">
         <v>640</v>
       </c>
-      <c r="B642" s="8">
+      <c r="B642" s="7">
         <v>51.3</v>
       </c>
     </row>
@@ -5822,7 +5941,7 @@
       <c r="A643">
         <v>641</v>
       </c>
-      <c r="B643" s="8">
+      <c r="B643" s="7">
         <v>51.3</v>
       </c>
     </row>
@@ -5830,7 +5949,7 @@
       <c r="A644">
         <v>642</v>
       </c>
-      <c r="B644" s="8">
+      <c r="B644" s="7">
         <v>51.3</v>
       </c>
     </row>
@@ -5838,7 +5957,7 @@
       <c r="A645">
         <v>643</v>
       </c>
-      <c r="B645" s="8">
+      <c r="B645" s="7">
         <v>51.3</v>
       </c>
     </row>
@@ -5846,7 +5965,7 @@
       <c r="A646">
         <v>644</v>
       </c>
-      <c r="B646" s="8">
+      <c r="B646" s="7">
         <v>51.3</v>
       </c>
     </row>
@@ -5854,7 +5973,7 @@
       <c r="A647">
         <v>645</v>
       </c>
-      <c r="B647" s="8">
+      <c r="B647" s="7">
         <v>51.4</v>
       </c>
     </row>
@@ -5862,7 +5981,7 @@
       <c r="A648">
         <v>646</v>
       </c>
-      <c r="B648" s="8">
+      <c r="B648" s="7">
         <v>51.4</v>
       </c>
     </row>
@@ -5870,7 +5989,7 @@
       <c r="A649">
         <v>647</v>
       </c>
-      <c r="B649" s="8">
+      <c r="B649" s="7">
         <v>51.4</v>
       </c>
     </row>
@@ -5878,7 +5997,7 @@
       <c r="A650">
         <v>648</v>
       </c>
-      <c r="B650" s="8">
+      <c r="B650" s="7">
         <v>51.5</v>
       </c>
     </row>
@@ -5886,7 +6005,7 @@
       <c r="A651">
         <v>649</v>
       </c>
-      <c r="B651" s="8">
+      <c r="B651" s="7">
         <v>51.5</v>
       </c>
     </row>
@@ -5894,7 +6013,7 @@
       <c r="A652">
         <v>650</v>
       </c>
-      <c r="B652" s="8">
+      <c r="B652" s="7">
         <v>51.5</v>
       </c>
     </row>
@@ -5902,7 +6021,7 @@
       <c r="A653">
         <v>651</v>
       </c>
-      <c r="B653" s="8">
+      <c r="B653" s="7">
         <v>51.5</v>
       </c>
     </row>
@@ -5910,7 +6029,7 @@
       <c r="A654">
         <v>652</v>
       </c>
-      <c r="B654" s="8">
+      <c r="B654" s="7">
         <v>51.5</v>
       </c>
     </row>
@@ -5918,7 +6037,7 @@
       <c r="A655">
         <v>653</v>
       </c>
-      <c r="B655" s="8">
+      <c r="B655" s="7">
         <v>51.6</v>
       </c>
     </row>
@@ -5926,7 +6045,7 @@
       <c r="A656">
         <v>654</v>
       </c>
-      <c r="B656" s="8">
+      <c r="B656" s="7">
         <v>51.6</v>
       </c>
     </row>
@@ -5934,7 +6053,7 @@
       <c r="A657">
         <v>655</v>
       </c>
-      <c r="B657" s="8">
+      <c r="B657" s="7">
         <v>51.6</v>
       </c>
     </row>
@@ -5942,7 +6061,7 @@
       <c r="A658">
         <v>656</v>
       </c>
-      <c r="B658" s="8">
+      <c r="B658" s="7">
         <v>51.7</v>
       </c>
     </row>
@@ -5950,7 +6069,7 @@
       <c r="A659">
         <v>657</v>
       </c>
-      <c r="B659" s="8">
+      <c r="B659" s="7">
         <v>51.7</v>
       </c>
     </row>
@@ -5958,7 +6077,7 @@
       <c r="A660">
         <v>658</v>
       </c>
-      <c r="B660" s="8">
+      <c r="B660" s="7">
         <v>51.7</v>
       </c>
     </row>
@@ -5966,7 +6085,7 @@
       <c r="A661">
         <v>659</v>
       </c>
-      <c r="B661" s="8">
+      <c r="B661" s="7">
         <v>51.8</v>
       </c>
     </row>
@@ -5974,7 +6093,7 @@
       <c r="A662">
         <v>660</v>
       </c>
-      <c r="B662" s="8">
+      <c r="B662" s="7">
         <v>51.8</v>
       </c>
     </row>
@@ -5982,7 +6101,7 @@
       <c r="A663">
         <v>661</v>
       </c>
-      <c r="B663" s="8">
+      <c r="B663" s="7">
         <v>51.8</v>
       </c>
     </row>
@@ -5990,7 +6109,7 @@
       <c r="A664">
         <v>662</v>
       </c>
-      <c r="B664" s="8">
+      <c r="B664" s="7">
         <v>51.8</v>
       </c>
     </row>
@@ -5998,7 +6117,7 @@
       <c r="A665">
         <v>663</v>
       </c>
-      <c r="B665" s="8">
+      <c r="B665" s="7">
         <v>51.9</v>
       </c>
     </row>
@@ -6006,7 +6125,7 @@
       <c r="A666">
         <v>664</v>
       </c>
-      <c r="B666" s="8">
+      <c r="B666" s="7">
         <v>51.9</v>
       </c>
     </row>
@@ -6014,7 +6133,7 @@
       <c r="A667">
         <v>665</v>
       </c>
-      <c r="B667" s="8">
+      <c r="B667" s="7">
         <v>51.9</v>
       </c>
     </row>
@@ -6022,7 +6141,7 @@
       <c r="A668">
         <v>666</v>
       </c>
-      <c r="B668" s="8">
+      <c r="B668" s="7">
         <v>51.9</v>
       </c>
     </row>
@@ -6030,7 +6149,7 @@
       <c r="A669">
         <v>667</v>
       </c>
-      <c r="B669" s="8">
+      <c r="B669" s="7">
         <v>51.9</v>
       </c>
     </row>
@@ -6038,7 +6157,7 @@
       <c r="A670">
         <v>668</v>
       </c>
-      <c r="B670" s="8">
+      <c r="B670" s="7">
         <v>52</v>
       </c>
     </row>
@@ -6046,7 +6165,7 @@
       <c r="A671">
         <v>669</v>
       </c>
-      <c r="B671" s="8">
+      <c r="B671" s="7">
         <v>52</v>
       </c>
     </row>
@@ -6054,7 +6173,7 @@
       <c r="A672">
         <v>670</v>
       </c>
-      <c r="B672" s="8">
+      <c r="B672" s="7">
         <v>52</v>
       </c>
     </row>
@@ -6062,7 +6181,7 @@
       <c r="A673">
         <v>671</v>
       </c>
-      <c r="B673" s="8">
+      <c r="B673" s="7">
         <v>52</v>
       </c>
     </row>
@@ -6070,7 +6189,7 @@
       <c r="A674">
         <v>672</v>
       </c>
-      <c r="B674" s="8">
+      <c r="B674" s="7">
         <v>52.1</v>
       </c>
     </row>
@@ -6078,7 +6197,7 @@
       <c r="A675">
         <v>673</v>
       </c>
-      <c r="B675" s="8">
+      <c r="B675" s="7">
         <v>52.1</v>
       </c>
     </row>
@@ -6086,7 +6205,7 @@
       <c r="A676">
         <v>674</v>
       </c>
-      <c r="B676" s="8">
+      <c r="B676" s="7">
         <v>52.2</v>
       </c>
     </row>
@@ -6094,7 +6213,7 @@
       <c r="A677">
         <v>675</v>
       </c>
-      <c r="B677" s="8">
+      <c r="B677" s="7">
         <v>52.2</v>
       </c>
     </row>
@@ -6102,7 +6221,7 @@
       <c r="A678">
         <v>676</v>
       </c>
-      <c r="B678" s="8">
+      <c r="B678" s="7">
         <v>52.2</v>
       </c>
     </row>
@@ -6110,7 +6229,7 @@
       <c r="A679">
         <v>677</v>
       </c>
-      <c r="B679" s="8">
+      <c r="B679" s="7">
         <v>52.2</v>
       </c>
     </row>
@@ -6118,7 +6237,7 @@
       <c r="A680">
         <v>678</v>
       </c>
-      <c r="B680" s="8">
+      <c r="B680" s="7">
         <v>52.2</v>
       </c>
     </row>
@@ -6126,7 +6245,7 @@
       <c r="A681">
         <v>679</v>
       </c>
-      <c r="B681" s="8">
+      <c r="B681" s="7">
         <v>52.3</v>
       </c>
     </row>
@@ -6134,7 +6253,7 @@
       <c r="A682">
         <v>680</v>
       </c>
-      <c r="B682" s="8">
+      <c r="B682" s="7">
         <v>52.3</v>
       </c>
     </row>
@@ -6142,7 +6261,7 @@
       <c r="A683">
         <v>681</v>
       </c>
-      <c r="B683" s="8">
+      <c r="B683" s="7">
         <v>52.3</v>
       </c>
     </row>
@@ -6150,7 +6269,7 @@
       <c r="A684">
         <v>682</v>
       </c>
-      <c r="B684" s="8">
+      <c r="B684" s="7">
         <v>52.3</v>
       </c>
     </row>
@@ -6158,7 +6277,7 @@
       <c r="A685">
         <v>683</v>
       </c>
-      <c r="B685" s="8">
+      <c r="B685" s="7">
         <v>52.3</v>
       </c>
     </row>
@@ -6166,7 +6285,7 @@
       <c r="A686">
         <v>684</v>
       </c>
-      <c r="B686" s="8">
+      <c r="B686" s="7">
         <v>52.4</v>
       </c>
     </row>
@@ -6174,7 +6293,7 @@
       <c r="A687">
         <v>685</v>
       </c>
-      <c r="B687" s="8">
+      <c r="B687" s="7">
         <v>52.4</v>
       </c>
     </row>
@@ -6182,7 +6301,7 @@
       <c r="A688">
         <v>686</v>
       </c>
-      <c r="B688" s="8">
+      <c r="B688" s="7">
         <v>52.4</v>
       </c>
     </row>
@@ -6190,7 +6309,7 @@
       <c r="A689">
         <v>687</v>
       </c>
-      <c r="B689" s="8">
+      <c r="B689" s="7">
         <v>52.4</v>
       </c>
     </row>
@@ -6198,7 +6317,7 @@
       <c r="A690">
         <v>688</v>
       </c>
-      <c r="B690" s="8">
+      <c r="B690" s="7">
         <v>52.5</v>
       </c>
     </row>
@@ -6206,7 +6325,7 @@
       <c r="A691">
         <v>689</v>
       </c>
-      <c r="B691" s="8">
+      <c r="B691" s="7">
         <v>52.5</v>
       </c>
     </row>
@@ -6214,7 +6333,7 @@
       <c r="A692">
         <v>690</v>
       </c>
-      <c r="B692" s="8">
+      <c r="B692" s="7">
         <v>52.6</v>
       </c>
     </row>
@@ -6222,7 +6341,7 @@
       <c r="A693">
         <v>691</v>
       </c>
-      <c r="B693" s="8">
+      <c r="B693" s="7">
         <v>52.6</v>
       </c>
     </row>
@@ -6230,7 +6349,7 @@
       <c r="A694">
         <v>692</v>
       </c>
-      <c r="B694" s="8">
+      <c r="B694" s="7">
         <v>52.6</v>
       </c>
     </row>
@@ -6238,7 +6357,7 @@
       <c r="A695">
         <v>693</v>
       </c>
-      <c r="B695" s="8">
+      <c r="B695" s="7">
         <v>52.6</v>
       </c>
     </row>
@@ -6246,7 +6365,7 @@
       <c r="A696">
         <v>694</v>
       </c>
-      <c r="B696" s="8">
+      <c r="B696" s="7">
         <v>52.6</v>
       </c>
     </row>
@@ -6254,7 +6373,7 @@
       <c r="A697">
         <v>695</v>
       </c>
-      <c r="B697" s="8">
+      <c r="B697" s="7">
         <v>52.6</v>
       </c>
     </row>
@@ -6262,7 +6381,7 @@
       <c r="A698">
         <v>696</v>
       </c>
-      <c r="B698" s="8">
+      <c r="B698" s="7">
         <v>52.7</v>
       </c>
     </row>
@@ -6270,7 +6389,7 @@
       <c r="A699">
         <v>697</v>
       </c>
-      <c r="B699" s="8">
+      <c r="B699" s="7">
         <v>52.7</v>
       </c>
     </row>
@@ -6278,7 +6397,7 @@
       <c r="A700">
         <v>698</v>
       </c>
-      <c r="B700" s="8">
+      <c r="B700" s="7">
         <v>52.7</v>
       </c>
     </row>
@@ -6286,7 +6405,7 @@
       <c r="A701">
         <v>699</v>
       </c>
-      <c r="B701" s="8">
+      <c r="B701" s="7">
         <v>52.7</v>
       </c>
     </row>
@@ -6294,7 +6413,7 @@
       <c r="A702">
         <v>700</v>
       </c>
-      <c r="B702" s="8">
+      <c r="B702" s="7">
         <v>52.7</v>
       </c>
     </row>
@@ -6302,7 +6421,7 @@
       <c r="A703">
         <v>701</v>
       </c>
-      <c r="B703" s="8">
+      <c r="B703" s="7">
         <v>52.8</v>
       </c>
     </row>
@@ -6310,7 +6429,7 @@
       <c r="A704">
         <v>702</v>
       </c>
-      <c r="B704" s="8">
+      <c r="B704" s="7">
         <v>52.8</v>
       </c>
     </row>
@@ -6318,7 +6437,7 @@
       <c r="A705">
         <v>703</v>
       </c>
-      <c r="B705" s="8">
+      <c r="B705" s="7">
         <v>52.8</v>
       </c>
     </row>
@@ -6326,7 +6445,7 @@
       <c r="A706">
         <v>704</v>
       </c>
-      <c r="B706" s="8">
+      <c r="B706" s="7">
         <v>52.9</v>
       </c>
     </row>
@@ -6334,7 +6453,7 @@
       <c r="A707">
         <v>705</v>
       </c>
-      <c r="B707" s="8">
+      <c r="B707" s="7">
         <v>52.9</v>
       </c>
     </row>
@@ -6342,7 +6461,7 @@
       <c r="A708">
         <v>706</v>
       </c>
-      <c r="B708" s="8">
+      <c r="B708" s="7">
         <v>52.9</v>
       </c>
     </row>
@@ -6350,7 +6469,7 @@
       <c r="A709">
         <v>707</v>
       </c>
-      <c r="B709" s="8">
+      <c r="B709" s="7">
         <v>52.9</v>
       </c>
     </row>
@@ -6358,7 +6477,7 @@
       <c r="A710">
         <v>708</v>
       </c>
-      <c r="B710" s="8">
+      <c r="B710" s="7">
         <v>52.9</v>
       </c>
     </row>
@@ -6366,7 +6485,7 @@
       <c r="A711">
         <v>709</v>
       </c>
-      <c r="B711" s="8">
+      <c r="B711" s="7">
         <v>53</v>
       </c>
     </row>
@@ -6374,7 +6493,7 @@
       <c r="A712">
         <v>710</v>
       </c>
-      <c r="B712" s="8">
+      <c r="B712" s="7">
         <v>53</v>
       </c>
     </row>
@@ -6382,7 +6501,7 @@
       <c r="A713">
         <v>711</v>
       </c>
-      <c r="B713" s="8">
+      <c r="B713" s="7">
         <v>53</v>
       </c>
     </row>
@@ -6390,7 +6509,7 @@
       <c r="A714">
         <v>712</v>
       </c>
-      <c r="B714" s="8">
+      <c r="B714" s="7">
         <v>53</v>
       </c>
     </row>
@@ -6398,7 +6517,7 @@
       <c r="A715">
         <v>713</v>
       </c>
-      <c r="B715" s="8">
+      <c r="B715" s="7">
         <v>53.1</v>
       </c>
     </row>
@@ -6406,7 +6525,7 @@
       <c r="A716">
         <v>714</v>
       </c>
-      <c r="B716" s="8">
+      <c r="B716" s="7">
         <v>53.1</v>
       </c>
     </row>
@@ -6414,7 +6533,7 @@
       <c r="A717">
         <v>715</v>
       </c>
-      <c r="B717" s="8">
+      <c r="B717" s="7">
         <v>53.1</v>
       </c>
     </row>
@@ -6422,7 +6541,7 @@
       <c r="A718">
         <v>716</v>
       </c>
-      <c r="B718" s="8">
+      <c r="B718" s="7">
         <v>53.2</v>
       </c>
     </row>
@@ -6430,7 +6549,7 @@
       <c r="A719">
         <v>717</v>
       </c>
-      <c r="B719" s="8">
+      <c r="B719" s="7">
         <v>53.2</v>
       </c>
     </row>
@@ -6438,7 +6557,7 @@
       <c r="A720">
         <v>718</v>
       </c>
-      <c r="B720" s="8">
+      <c r="B720" s="7">
         <v>53.2</v>
       </c>
     </row>
@@ -6446,7 +6565,7 @@
       <c r="A721">
         <v>719</v>
       </c>
-      <c r="B721" s="8">
+      <c r="B721" s="7">
         <v>53.2</v>
       </c>
     </row>
@@ -6454,7 +6573,7 @@
       <c r="A722">
         <v>720</v>
       </c>
-      <c r="B722" s="8">
+      <c r="B722" s="7">
         <v>53.3</v>
       </c>
     </row>
@@ -6462,7 +6581,7 @@
       <c r="A723">
         <v>721</v>
       </c>
-      <c r="B723" s="8">
+      <c r="B723" s="7">
         <v>53.3</v>
       </c>
     </row>
@@ -6470,7 +6589,7 @@
       <c r="A724">
         <v>722</v>
       </c>
-      <c r="B724" s="8">
+      <c r="B724" s="7">
         <v>53.3</v>
       </c>
     </row>
@@ -6478,7 +6597,7 @@
       <c r="A725">
         <v>723</v>
       </c>
-      <c r="B725" s="8">
+      <c r="B725" s="7">
         <v>53.3</v>
       </c>
     </row>
@@ -6486,7 +6605,7 @@
       <c r="A726">
         <v>724</v>
       </c>
-      <c r="B726" s="8">
+      <c r="B726" s="7">
         <v>53.4</v>
       </c>
     </row>
@@ -6494,7 +6613,7 @@
       <c r="A727">
         <v>725</v>
       </c>
-      <c r="B727" s="8">
+      <c r="B727" s="7">
         <v>53.4</v>
       </c>
     </row>
@@ -6502,7 +6621,7 @@
       <c r="A728">
         <v>726</v>
       </c>
-      <c r="B728" s="8">
+      <c r="B728" s="7">
         <v>53.5</v>
       </c>
     </row>
@@ -6510,7 +6629,7 @@
       <c r="A729">
         <v>727</v>
       </c>
-      <c r="B729" s="8">
+      <c r="B729" s="7">
         <v>53.5</v>
       </c>
     </row>
@@ -6518,7 +6637,7 @@
       <c r="A730">
         <v>728</v>
       </c>
-      <c r="B730" s="8">
+      <c r="B730" s="7">
         <v>53.5</v>
       </c>
     </row>
@@ -6526,7 +6645,7 @@
       <c r="A731">
         <v>729</v>
       </c>
-      <c r="B731" s="8">
+      <c r="B731" s="7">
         <v>53.5</v>
       </c>
     </row>
@@ -6534,7 +6653,7 @@
       <c r="A732">
         <v>730</v>
       </c>
-      <c r="B732" s="8">
+      <c r="B732" s="7">
         <v>53.5</v>
       </c>
     </row>
@@ -6542,7 +6661,7 @@
       <c r="A733">
         <v>731</v>
       </c>
-      <c r="B733" s="8">
+      <c r="B733" s="7">
         <v>53.6</v>
       </c>
     </row>
@@ -6550,7 +6669,7 @@
       <c r="A734">
         <v>732</v>
       </c>
-      <c r="B734" s="8">
+      <c r="B734" s="7">
         <v>53.6</v>
       </c>
     </row>
@@ -6558,7 +6677,7 @@
       <c r="A735">
         <v>733</v>
       </c>
-      <c r="B735" s="8">
+      <c r="B735" s="7">
         <v>53.6</v>
       </c>
     </row>
@@ -6566,7 +6685,7 @@
       <c r="A736">
         <v>734</v>
       </c>
-      <c r="B736" s="8">
+      <c r="B736" s="7">
         <v>53.7</v>
       </c>
     </row>
@@ -6574,7 +6693,7 @@
       <c r="A737">
         <v>735</v>
       </c>
-      <c r="B737" s="8">
+      <c r="B737" s="7">
         <v>53.7</v>
       </c>
     </row>
@@ -6582,7 +6701,7 @@
       <c r="A738">
         <v>736</v>
       </c>
-      <c r="B738" s="8">
+      <c r="B738" s="7">
         <v>53.7</v>
       </c>
     </row>
@@ -6590,7 +6709,7 @@
       <c r="A739">
         <v>737</v>
       </c>
-      <c r="B739" s="8">
+      <c r="B739" s="7">
         <v>53.8</v>
       </c>
     </row>
@@ -6598,7 +6717,7 @@
       <c r="A740">
         <v>738</v>
       </c>
-      <c r="B740" s="8">
+      <c r="B740" s="7">
         <v>53.8</v>
       </c>
     </row>
@@ -6606,7 +6725,7 @@
       <c r="A741">
         <v>739</v>
       </c>
-      <c r="B741" s="8">
+      <c r="B741" s="7">
         <v>53.8</v>
       </c>
     </row>
@@ -6614,7 +6733,7 @@
       <c r="A742">
         <v>740</v>
       </c>
-      <c r="B742" s="8">
+      <c r="B742" s="7">
         <v>53.8</v>
       </c>
     </row>
@@ -6622,7 +6741,7 @@
       <c r="A743">
         <v>741</v>
       </c>
-      <c r="B743" s="8">
+      <c r="B743" s="7">
         <v>53.9</v>
       </c>
     </row>
@@ -6630,7 +6749,7 @@
       <c r="A744">
         <v>742</v>
       </c>
-      <c r="B744" s="8">
+      <c r="B744" s="7">
         <v>53.9</v>
       </c>
     </row>
@@ -6638,7 +6757,7 @@
       <c r="A745">
         <v>743</v>
       </c>
-      <c r="B745" s="8">
+      <c r="B745" s="7">
         <v>53.9</v>
       </c>
     </row>
@@ -6646,7 +6765,7 @@
       <c r="A746">
         <v>744</v>
       </c>
-      <c r="B746" s="8">
+      <c r="B746" s="7">
         <v>53.9</v>
       </c>
     </row>
@@ -6654,7 +6773,7 @@
       <c r="A747">
         <v>745</v>
       </c>
-      <c r="B747" s="8">
+      <c r="B747" s="7">
         <v>54</v>
       </c>
     </row>
@@ -6662,7 +6781,7 @@
       <c r="A748">
         <v>746</v>
       </c>
-      <c r="B748" s="8">
+      <c r="B748" s="7">
         <v>53.9</v>
       </c>
     </row>
@@ -6670,7 +6789,7 @@
       <c r="A749">
         <v>747</v>
       </c>
-      <c r="B749" s="8">
+      <c r="B749" s="7">
         <v>54</v>
       </c>
     </row>
@@ -6678,7 +6797,7 @@
       <c r="A750">
         <v>748</v>
       </c>
-      <c r="B750" s="8">
+      <c r="B750" s="7">
         <v>54</v>
       </c>
     </row>
@@ -6686,7 +6805,7 @@
       <c r="A751">
         <v>749</v>
       </c>
-      <c r="B751" s="8">
+      <c r="B751" s="7">
         <v>54.1</v>
       </c>
     </row>
@@ -6694,7 +6813,7 @@
       <c r="A752">
         <v>750</v>
       </c>
-      <c r="B752" s="8">
+      <c r="B752" s="7">
         <v>54.1</v>
       </c>
     </row>
@@ -6702,7 +6821,7 @@
       <c r="A753">
         <v>751</v>
       </c>
-      <c r="B753" s="8">
+      <c r="B753" s="7">
         <v>54.1</v>
       </c>
     </row>
@@ -6710,7 +6829,7 @@
       <c r="A754">
         <v>752</v>
       </c>
-      <c r="B754" s="8">
+      <c r="B754" s="7">
         <v>54.1</v>
       </c>
     </row>
@@ -6718,7 +6837,7 @@
       <c r="A755">
         <v>753</v>
       </c>
-      <c r="B755" s="8">
+      <c r="B755" s="7">
         <v>54.2</v>
       </c>
     </row>
@@ -6726,7 +6845,7 @@
       <c r="A756">
         <v>754</v>
       </c>
-      <c r="B756" s="8">
+      <c r="B756" s="7">
         <v>54.2</v>
       </c>
     </row>
@@ -6734,7 +6853,7 @@
       <c r="A757">
         <v>755</v>
       </c>
-      <c r="B757" s="8">
+      <c r="B757" s="7">
         <v>54.2</v>
       </c>
     </row>
@@ -6742,7 +6861,7 @@
       <c r="A758">
         <v>756</v>
       </c>
-      <c r="B758" s="8">
+      <c r="B758" s="7">
         <v>54.3</v>
       </c>
     </row>
@@ -6750,7 +6869,7 @@
       <c r="A759">
         <v>757</v>
       </c>
-      <c r="B759" s="8">
+      <c r="B759" s="7">
         <v>54.3</v>
       </c>
     </row>
@@ -6758,7 +6877,7 @@
       <c r="A760">
         <v>758</v>
       </c>
-      <c r="B760" s="8">
+      <c r="B760" s="7">
         <v>54.3</v>
       </c>
     </row>
@@ -6766,7 +6885,7 @@
       <c r="A761">
         <v>759</v>
       </c>
-      <c r="B761" s="8">
+      <c r="B761" s="7">
         <v>54.4</v>
       </c>
     </row>
@@ -6774,7 +6893,7 @@
       <c r="A762">
         <v>760</v>
       </c>
-      <c r="B762" s="8">
+      <c r="B762" s="7">
         <v>54.4</v>
       </c>
     </row>
@@ -6782,7 +6901,7 @@
       <c r="A763">
         <v>761</v>
       </c>
-      <c r="B763" s="8">
+      <c r="B763" s="7">
         <v>54.4</v>
       </c>
     </row>
@@ -6790,7 +6909,7 @@
       <c r="A764">
         <v>762</v>
       </c>
-      <c r="B764" s="8">
+      <c r="B764" s="7">
         <v>54.4</v>
       </c>
     </row>
@@ -6798,7 +6917,7 @@
       <c r="A765">
         <v>763</v>
       </c>
-      <c r="B765" s="8">
+      <c r="B765" s="7">
         <v>54.4</v>
       </c>
     </row>
@@ -6806,7 +6925,7 @@
       <c r="A766">
         <v>764</v>
       </c>
-      <c r="B766" s="8">
+      <c r="B766" s="7">
         <v>54.5</v>
       </c>
     </row>
@@ -6814,7 +6933,7 @@
       <c r="A767">
         <v>765</v>
       </c>
-      <c r="B767" s="8">
+      <c r="B767" s="7">
         <v>54.5</v>
       </c>
     </row>
@@ -6822,7 +6941,7 @@
       <c r="A768">
         <v>766</v>
       </c>
-      <c r="B768" s="8">
+      <c r="B768" s="7">
         <v>54.5</v>
       </c>
     </row>
@@ -6830,7 +6949,7 @@
       <c r="A769">
         <v>767</v>
       </c>
-      <c r="B769" s="8">
+      <c r="B769" s="7">
         <v>54.6</v>
       </c>
     </row>
@@ -6838,7 +6957,7 @@
       <c r="A770">
         <v>768</v>
       </c>
-      <c r="B770" s="8">
+      <c r="B770" s="7">
         <v>54.6</v>
       </c>
     </row>
@@ -6846,7 +6965,7 @@
       <c r="A771">
         <v>769</v>
       </c>
-      <c r="B771" s="8">
+      <c r="B771" s="7">
         <v>54.6</v>
       </c>
     </row>
@@ -6854,7 +6973,7 @@
       <c r="A772">
         <v>770</v>
       </c>
-      <c r="B772" s="8">
+      <c r="B772" s="7">
         <v>54.7</v>
       </c>
     </row>
@@ -6862,7 +6981,7 @@
       <c r="A773">
         <v>771</v>
       </c>
-      <c r="B773" s="8">
+      <c r="B773" s="7">
         <v>54.7</v>
       </c>
     </row>
@@ -6870,7 +6989,7 @@
       <c r="A774">
         <v>772</v>
       </c>
-      <c r="B774" s="8">
+      <c r="B774" s="7">
         <v>54.7</v>
       </c>
     </row>
@@ -6878,7 +6997,7 @@
       <c r="A775">
         <v>773</v>
       </c>
-      <c r="B775" s="8">
+      <c r="B775" s="7">
         <v>54.8</v>
       </c>
     </row>
@@ -6886,7 +7005,7 @@
       <c r="A776">
         <v>774</v>
       </c>
-      <c r="B776" s="8">
+      <c r="B776" s="7">
         <v>54.8</v>
       </c>
     </row>
@@ -6894,7 +7013,7 @@
       <c r="A777">
         <v>775</v>
       </c>
-      <c r="B777" s="8">
+      <c r="B777" s="7">
         <v>54.8</v>
       </c>
     </row>
@@ -6902,7 +7021,7 @@
       <c r="A778">
         <v>776</v>
       </c>
-      <c r="B778" s="8">
+      <c r="B778" s="7">
         <v>54.9</v>
       </c>
     </row>
@@ -6910,7 +7029,7 @@
       <c r="A779">
         <v>777</v>
       </c>
-      <c r="B779" s="8">
+      <c r="B779" s="7">
         <v>54.9</v>
       </c>
     </row>
@@ -6918,7 +7037,7 @@
       <c r="A780">
         <v>778</v>
       </c>
-      <c r="B780" s="8">
+      <c r="B780" s="7">
         <v>54.9</v>
       </c>
     </row>
@@ -6926,7 +7045,7 @@
       <c r="A781">
         <v>779</v>
       </c>
-      <c r="B781" s="8">
+      <c r="B781" s="7">
         <v>55</v>
       </c>
     </row>
@@ -6934,7 +7053,7 @@
       <c r="A782">
         <v>780</v>
       </c>
-      <c r="B782" s="8">
+      <c r="B782" s="7">
         <v>55</v>
       </c>
     </row>
@@ -6942,7 +7061,7 @@
       <c r="A783">
         <v>781</v>
       </c>
-      <c r="B783" s="8">
+      <c r="B783" s="7">
         <v>55</v>
       </c>
     </row>
@@ -6950,7 +7069,7 @@
       <c r="A784">
         <v>782</v>
       </c>
-      <c r="B784" s="8">
+      <c r="B784" s="7">
         <v>55</v>
       </c>
     </row>
@@ -6958,7 +7077,7 @@
       <c r="A785">
         <v>783</v>
       </c>
-      <c r="B785" s="8">
+      <c r="B785" s="7">
         <v>55.1</v>
       </c>
     </row>
@@ -6966,7 +7085,7 @@
       <c r="A786">
         <v>784</v>
       </c>
-      <c r="B786" s="8">
+      <c r="B786" s="7">
         <v>55.1</v>
       </c>
     </row>
@@ -6974,7 +7093,7 @@
       <c r="A787">
         <v>785</v>
       </c>
-      <c r="B787" s="8">
+      <c r="B787" s="7">
         <v>55.1</v>
       </c>
     </row>
@@ -6982,7 +7101,7 @@
       <c r="A788">
         <v>786</v>
       </c>
-      <c r="B788" s="8">
+      <c r="B788" s="7">
         <v>55.2</v>
       </c>
     </row>
@@ -6990,7 +7109,7 @@
       <c r="A789">
         <v>787</v>
       </c>
-      <c r="B789" s="8">
+      <c r="B789" s="7">
         <v>55.2</v>
       </c>
     </row>
@@ -6998,7 +7117,7 @@
       <c r="A790">
         <v>788</v>
       </c>
-      <c r="B790" s="8">
+      <c r="B790" s="7">
         <v>55.2</v>
       </c>
     </row>
@@ -7006,7 +7125,7 @@
       <c r="A791">
         <v>789</v>
       </c>
-      <c r="B791" s="8">
+      <c r="B791" s="7">
         <v>55.3</v>
       </c>
     </row>
@@ -7014,7 +7133,7 @@
       <c r="A792">
         <v>790</v>
       </c>
-      <c r="B792" s="8">
+      <c r="B792" s="7">
         <v>55.3</v>
       </c>
     </row>
@@ -7022,7 +7141,7 @@
       <c r="A793">
         <v>791</v>
       </c>
-      <c r="B793" s="8">
+      <c r="B793" s="7">
         <v>55.3</v>
       </c>
     </row>
@@ -7030,7 +7149,7 @@
       <c r="A794">
         <v>792</v>
       </c>
-      <c r="B794" s="8">
+      <c r="B794" s="7">
         <v>55.3</v>
       </c>
     </row>
@@ -7038,7 +7157,7 @@
       <c r="A795">
         <v>793</v>
       </c>
-      <c r="B795" s="8">
+      <c r="B795" s="7">
         <v>55.4</v>
       </c>
     </row>
@@ -7046,7 +7165,7 @@
       <c r="A796">
         <v>794</v>
       </c>
-      <c r="B796" s="8">
+      <c r="B796" s="7">
         <v>55.4</v>
       </c>
     </row>
@@ -7054,7 +7173,7 @@
       <c r="A797">
         <v>795</v>
       </c>
-      <c r="B797" s="8">
+      <c r="B797" s="7">
         <v>55.4</v>
       </c>
     </row>
@@ -7062,7 +7181,7 @@
       <c r="A798">
         <v>796</v>
       </c>
-      <c r="B798" s="8">
+      <c r="B798" s="7">
         <v>55.5</v>
       </c>
     </row>
@@ -7070,7 +7189,7 @@
       <c r="A799">
         <v>797</v>
       </c>
-      <c r="B799" s="8">
+      <c r="B799" s="7">
         <v>55.5</v>
       </c>
     </row>
@@ -7078,7 +7197,7 @@
       <c r="A800">
         <v>798</v>
       </c>
-      <c r="B800" s="8">
+      <c r="B800" s="7">
         <v>55.6</v>
       </c>
     </row>
@@ -7086,7 +7205,7 @@
       <c r="A801">
         <v>799</v>
       </c>
-      <c r="B801" s="8">
+      <c r="B801" s="7">
         <v>55.6</v>
       </c>
     </row>
@@ -7094,7 +7213,7 @@
       <c r="A802">
         <v>800</v>
       </c>
-      <c r="B802" s="8">
+      <c r="B802" s="7">
         <v>55.6</v>
       </c>
     </row>
@@ -7102,7 +7221,7 @@
       <c r="A803">
         <v>801</v>
       </c>
-      <c r="B803" s="8">
+      <c r="B803" s="7">
         <v>55.6</v>
       </c>
     </row>
@@ -7110,7 +7229,7 @@
       <c r="A804">
         <v>802</v>
       </c>
-      <c r="B804" s="8">
+      <c r="B804" s="7">
         <v>55.6</v>
       </c>
     </row>
@@ -7118,15 +7237,263 @@
       <c r="A805">
         <v>803</v>
       </c>
-      <c r="B805" s="8">
+      <c r="B805" s="7">
         <v>55.7</v>
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B806" s="7"/>
+      <c r="B806" s="6"/>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B807" s="7"/>
+      <c r="B807" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F113E6F6-2477-4789-8A27-57AFD2F379D3}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.47265625" customWidth="1"/>
+    <col min="2" max="2" width="10.578125" customWidth="1"/>
+    <col min="7" max="7" width="15.41796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.23699999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.36699999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.41799999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.443</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30E8FD8-0EBB-4177-9DEF-F00F415B90A1}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="11.47265625" customWidth="1"/>
+    <col min="2" max="2" width="10.578125" customWidth="1"/>
+    <col min="7" max="7" width="15.41796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="B2" s="8">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="B3" s="8">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="B4" s="8">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="B5" s="8">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.1245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
